--- a/excel_templates/templates.xlsx
+++ b/excel_templates/templates.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Футбол исход" sheetId="1" state="visible" r:id="rId3"/>
@@ -1128,7 +1128,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999"/>
+        <fgColor theme="8" tint="0.7998"/>
         <bgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
@@ -1146,7 +1146,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999"/>
+        <fgColor theme="4" tint="0.7998"/>
         <bgColor rgb="FFDAE3F3"/>
       </patternFill>
     </fill>
@@ -1158,13 +1158,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999"/>
+        <fgColor theme="6" tint="0.7998"/>
         <bgColor rgb="FFEEECE1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999"/>
+        <fgColor theme="5" tint="0.7998"/>
         <bgColor rgb="FFF8D9C0"/>
       </patternFill>
     </fill>
@@ -1278,7 +1278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999"/>
+        <fgColor theme="3" tint="0.7998"/>
         <bgColor rgb="FFC8E1FC"/>
       </patternFill>
     </fill>
@@ -1395,6 +1395,13 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right style="thin"/>
       <top/>
@@ -1431,13 +1438,6 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="medium"/>
@@ -1519,991 +1519,991 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="24" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="26" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="26" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="24" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="25" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="25" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="24" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="24" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="25" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="26" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="26" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="24" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="24" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="23" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="23" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="31" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="31" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="31" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="31" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="32" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="32" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="28" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2761,13 +2761,27 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BL9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="100.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="46" min="46" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="47" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="50" min="50" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="51" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="54" min="54" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="55" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="100.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.56"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3089,7 +3103,7 @@
       <c r="AW6" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="AX6" s="46" t="n">
+      <c r="AX6" s="18" t="n">
         <v>130</v>
       </c>
       <c r="AY6" s="63" t="n">
@@ -3101,31 +3115,31 @@
       <c r="BA6" s="65" t="n">
         <v>49</v>
       </c>
-      <c r="BB6" s="46" t="n">
+      <c r="BB6" s="18" t="n">
         <v>131</v>
       </c>
-      <c r="BC6" s="44" t="n">
+      <c r="BC6" s="66" t="n">
         <v>50</v>
       </c>
-      <c r="BD6" s="45" t="n">
+      <c r="BD6" s="66" t="n">
         <v>51</v>
       </c>
-      <c r="BE6" s="46" t="n">
+      <c r="BE6" s="66" t="n">
         <v>52</v>
       </c>
-      <c r="BF6" s="45" t="n">
+      <c r="BF6" s="66" t="n">
         <v>53</v>
       </c>
-      <c r="BG6" s="46" t="n">
+      <c r="BG6" s="66" t="n">
         <v>54</v>
       </c>
-      <c r="BH6" s="45" t="n">
+      <c r="BH6" s="66" t="n">
         <v>55</v>
       </c>
-      <c r="BI6" s="46" t="n">
+      <c r="BI6" s="66" t="n">
         <v>56</v>
       </c>
-      <c r="BJ6" s="45" t="n">
+      <c r="BJ6" s="66" t="n">
         <v>57</v>
       </c>
       <c r="BK6" s="66" t="n">
@@ -3264,28 +3278,28 @@
       <c r="BC7" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="BD7" s="100" t="s">
+      <c r="BD7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="BE7" s="100" t="s">
+      <c r="BE7" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="BF7" s="100" t="s">
+      <c r="BF7" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="BG7" s="100" t="s">
+      <c r="BG7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="BH7" s="100" t="s">
+      <c r="BH7" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="BI7" s="100" t="s">
+      <c r="BI7" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="BJ7" s="100" t="s">
+      <c r="BJ7" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="BK7" s="101" t="s">
+      <c r="BK7" s="100" t="s">
         <v>61</v>
       </c>
       <c r="BL7" s="31"/>
@@ -3295,190 +3309,190 @@
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="102" t="s">
+      <c r="G8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="102" t="s">
+      <c r="H8" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="102" t="s">
+      <c r="I8" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="102" t="s">
+      <c r="J8" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="102" t="s">
+      <c r="K8" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="102" t="s">
+      <c r="L8" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="102" t="s">
+      <c r="M8" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="102" t="s">
+      <c r="N8" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="102" t="s">
+      <c r="O8" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="102" t="s">
+      <c r="P8" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="102" t="s">
+      <c r="Q8" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="102" t="s">
+      <c r="R8" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="102" t="s">
+      <c r="S8" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="T8" s="102" t="s">
+      <c r="T8" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="U8" s="102" t="s">
+      <c r="U8" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="V8" s="102" t="s">
+      <c r="V8" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="102" t="s">
+      <c r="W8" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="102" t="s">
+      <c r="X8" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="102" t="s">
+      <c r="Y8" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="102" t="s">
+      <c r="Z8" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="AA8" s="102" t="s">
+      <c r="AA8" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="AB8" s="102" t="s">
+      <c r="AB8" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AC8" s="102" t="s">
+      <c r="AC8" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="AD8" s="102" t="s">
+      <c r="AD8" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="AE8" s="102" t="s">
+      <c r="AE8" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="AF8" s="102" t="s">
+      <c r="AF8" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="102" t="s">
+      <c r="AG8" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="AH8" s="102" t="s">
+      <c r="AH8" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="102" t="s">
+      <c r="AI8" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="AJ8" s="102" t="s">
+      <c r="AJ8" s="101" t="s">
         <v>96</v>
       </c>
-      <c r="AK8" s="102" t="s">
+      <c r="AK8" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="AL8" s="102" t="s">
+      <c r="AL8" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="AM8" s="102" t="s">
+      <c r="AM8" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="AN8" s="102" t="s">
+      <c r="AN8" s="101" t="s">
         <v>100</v>
       </c>
-      <c r="AO8" s="102" t="s">
+      <c r="AO8" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="AP8" s="102" t="s">
+      <c r="AP8" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="AQ8" s="102" t="s">
+      <c r="AQ8" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="AR8" s="102" t="s">
+      <c r="AR8" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="AS8" s="102" t="s">
+      <c r="AS8" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="AT8" s="102" t="s">
+      <c r="AT8" s="101" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="102" t="s">
+      <c r="AU8" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="AV8" s="102" t="s">
+      <c r="AV8" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="AW8" s="102" t="s">
+      <c r="AW8" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="AX8" s="102" t="s">
+      <c r="AX8" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="AY8" s="102" t="s">
+      <c r="AY8" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="AZ8" s="102" t="s">
+      <c r="AZ8" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="BA8" s="102" t="s">
+      <c r="BA8" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="BB8" s="102" t="s">
+      <c r="BB8" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="BC8" s="102" t="s">
+      <c r="BC8" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="BD8" s="102" t="s">
+      <c r="BD8" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="BE8" s="102" t="s">
+      <c r="BE8" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="BF8" s="102" t="s">
+      <c r="BF8" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="BG8" s="102" t="s">
+      <c r="BG8" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="BH8" s="102" t="s">
+      <c r="BH8" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="BI8" s="102" t="s">
+      <c r="BI8" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="BJ8" s="102" t="s">
+      <c r="BJ8" s="101" t="s">
         <v>122</v>
       </c>
-      <c r="BK8" s="102" t="s">
+      <c r="BK8" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="BL8" s="102" t="s">
+      <c r="BL8" s="101" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3527,12 +3541,26 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BP9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="100.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="46" min="46" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="47" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="50" min="50" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="51" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="54" min="54" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="55" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="100.67"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3800,13 +3828,13 @@
       <c r="AE6" s="49" t="n">
         <v>34</v>
       </c>
-      <c r="AF6" s="46" t="n">
+      <c r="AF6" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="AG6" s="45" t="n">
+      <c r="AG6" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="AH6" s="46" t="n">
+      <c r="AH6" s="18" t="n">
         <v>30</v>
       </c>
       <c r="AI6" s="51" t="n">
@@ -3824,7 +3852,7 @@
       <c r="AM6" s="55" t="n">
         <v>39</v>
       </c>
-      <c r="AN6" s="46" t="n">
+      <c r="AN6" s="18" t="n">
         <v>127</v>
       </c>
       <c r="AO6" s="56" t="n">
@@ -3833,7 +3861,7 @@
       <c r="AP6" s="57" t="n">
         <v>114</v>
       </c>
-      <c r="AQ6" s="46" t="n">
+      <c r="AQ6" s="18" t="n">
         <v>128</v>
       </c>
       <c r="AR6" s="58" t="n">
@@ -3842,7 +3870,7 @@
       <c r="AS6" s="59" t="n">
         <v>95</v>
       </c>
-      <c r="AT6" s="46" t="n">
+      <c r="AT6" s="18" t="n">
         <v>129</v>
       </c>
       <c r="AU6" s="60" t="n">
@@ -3854,7 +3882,7 @@
       <c r="AW6" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="AX6" s="46" t="n">
+      <c r="AX6" s="18" t="n">
         <v>130</v>
       </c>
       <c r="AY6" s="63" t="n">
@@ -3866,31 +3894,31 @@
       <c r="BA6" s="65" t="n">
         <v>49</v>
       </c>
-      <c r="BB6" s="46" t="n">
+      <c r="BB6" s="18" t="n">
         <v>131</v>
       </c>
-      <c r="BC6" s="44" t="n">
+      <c r="BC6" s="66" t="n">
         <v>50</v>
       </c>
-      <c r="BD6" s="45" t="n">
+      <c r="BD6" s="66" t="n">
         <v>51</v>
       </c>
-      <c r="BE6" s="46" t="n">
+      <c r="BE6" s="66" t="n">
         <v>52</v>
       </c>
-      <c r="BF6" s="45" t="n">
+      <c r="BF6" s="66" t="n">
         <v>53</v>
       </c>
-      <c r="BG6" s="46" t="n">
+      <c r="BG6" s="66" t="n">
         <v>54</v>
       </c>
-      <c r="BH6" s="45" t="n">
+      <c r="BH6" s="66" t="n">
         <v>55</v>
       </c>
-      <c r="BI6" s="46" t="n">
+      <c r="BI6" s="66" t="n">
         <v>56</v>
       </c>
-      <c r="BJ6" s="45" t="n">
+      <c r="BJ6" s="66" t="n">
         <v>57</v>
       </c>
       <c r="BK6" s="66" t="n">
@@ -4026,230 +4054,226 @@
         <v>44</v>
       </c>
       <c r="BB7" s="18"/>
-      <c r="BC7" s="99" t="s">
+      <c r="BC7" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="BD7" s="100" t="s">
+      <c r="BD7" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="BE7" s="100" t="s">
+      <c r="BE7" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="BF7" s="100" t="s">
+      <c r="BF7" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="BG7" s="100" t="s">
+      <c r="BG7" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="BH7" s="100" t="s">
+      <c r="BH7" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="BI7" s="100" t="s">
+      <c r="BI7" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="BJ7" s="100" t="s">
+      <c r="BJ7" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="BK7" s="101" t="s">
+      <c r="BK7" s="104" t="s">
         <v>61</v>
       </c>
       <c r="BL7" s="31"/>
     </row>
-    <row r="8" s="103" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="105" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="102" t="s">
+      <c r="G8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="102" t="s">
+      <c r="H8" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="102" t="s">
+      <c r="I8" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="102" t="s">
+      <c r="J8" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="102" t="s">
+      <c r="K8" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="102" t="s">
+      <c r="L8" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="102" t="s">
+      <c r="M8" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="102" t="s">
+      <c r="N8" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="102" t="s">
+      <c r="O8" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="102" t="s">
+      <c r="P8" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="102" t="s">
+      <c r="Q8" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="102" t="s">
+      <c r="R8" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="102" t="s">
+      <c r="S8" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="T8" s="102" t="s">
+      <c r="T8" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="U8" s="102" t="s">
+      <c r="U8" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="V8" s="102" t="s">
+      <c r="V8" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="102" t="s">
+      <c r="W8" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="102" t="s">
+      <c r="X8" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="102" t="s">
+      <c r="Y8" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="102" t="s">
+      <c r="Z8" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="AA8" s="102" t="s">
+      <c r="AA8" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="AB8" s="102" t="s">
+      <c r="AB8" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AC8" s="102" t="s">
+      <c r="AC8" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="AD8" s="102" t="s">
+      <c r="AD8" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="AE8" s="102" t="s">
+      <c r="AE8" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="AF8" s="102" t="s">
+      <c r="AF8" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="102" t="s">
+      <c r="AG8" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="AH8" s="102" t="s">
+      <c r="AH8" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="102" t="s">
+      <c r="AI8" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="AJ8" s="102" t="s">
+      <c r="AJ8" s="101" t="s">
         <v>96</v>
       </c>
-      <c r="AK8" s="102" t="s">
+      <c r="AK8" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="AL8" s="102" t="s">
+      <c r="AL8" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="AM8" s="102" t="s">
+      <c r="AM8" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="AN8" s="102" t="s">
+      <c r="AN8" s="101" t="s">
         <v>100</v>
       </c>
-      <c r="AO8" s="102" t="s">
+      <c r="AO8" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="AP8" s="102" t="s">
+      <c r="AP8" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="AQ8" s="102" t="s">
+      <c r="AQ8" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="AR8" s="102" t="s">
+      <c r="AR8" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="AS8" s="102" t="s">
+      <c r="AS8" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="AT8" s="102" t="s">
+      <c r="AT8" s="101" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="102" t="s">
+      <c r="AU8" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="AV8" s="102" t="s">
+      <c r="AV8" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="AW8" s="102" t="s">
+      <c r="AW8" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="AX8" s="102" t="s">
+      <c r="AX8" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="AY8" s="102" t="s">
+      <c r="AY8" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="AZ8" s="102" t="s">
+      <c r="AZ8" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="BA8" s="102" t="s">
+      <c r="BA8" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="BB8" s="102" t="s">
+      <c r="BB8" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="BC8" s="102" t="s">
+      <c r="BC8" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="BD8" s="102" t="s">
+      <c r="BD8" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="BE8" s="102" t="s">
+      <c r="BE8" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="BF8" s="102" t="s">
+      <c r="BF8" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="BG8" s="102" t="s">
+      <c r="BG8" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="BH8" s="102" t="s">
+      <c r="BH8" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="BI8" s="102" t="s">
+      <c r="BI8" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="BJ8" s="102" t="s">
+      <c r="BJ8" s="101" t="s">
         <v>122</v>
       </c>
-      <c r="BK8" s="102" t="s">
+      <c r="BK8" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="BL8" s="102" t="s">
+      <c r="BL8" s="101" t="s">
         <v>124</v>
       </c>
-      <c r="BM8" s="0"/>
-      <c r="BN8" s="0"/>
-      <c r="BO8" s="0"/>
-      <c r="BP8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
@@ -4365,13 +4389,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BP9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="100.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="50" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="56" min="56" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="57" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="60" min="60" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="61" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="64" min="64" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="65" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="67" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="100.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.56"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4464,28 +4503,28 @@
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
-      <c r="U5" s="104" t="s">
+      <c r="U5" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="V5" s="104"/>
-      <c r="W5" s="104"/>
-      <c r="X5" s="105" t="s">
+      <c r="V5" s="106"/>
+      <c r="W5" s="106"/>
+      <c r="X5" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
+      <c r="Y5" s="107"/>
+      <c r="Z5" s="107"/>
       <c r="AA5" s="18" t="s">
         <v>11</v>
       </c>
       <c r="AB5" s="18"/>
-      <c r="AC5" s="106" t="s">
+      <c r="AC5" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="AD5" s="106"/>
-      <c r="AE5" s="107" t="s">
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="AF5" s="107"/>
+      <c r="AF5" s="109"/>
       <c r="AG5" s="20" t="s">
         <v>14</v>
       </c>
@@ -4499,18 +4538,18 @@
       </c>
       <c r="AL5" s="22"/>
       <c r="AM5" s="22"/>
-      <c r="AN5" s="108" t="s">
+      <c r="AN5" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="AO5" s="108"/>
-      <c r="AP5" s="108" t="s">
+      <c r="AO5" s="110"/>
+      <c r="AP5" s="110" t="s">
         <v>18</v>
       </c>
       <c r="AQ5" s="23" t="s">
         <v>129</v>
       </c>
       <c r="AR5" s="23"/>
-      <c r="AS5" s="109" t="s">
+      <c r="AS5" s="111" t="s">
         <v>130</v>
       </c>
       <c r="AT5" s="24" t="s">
@@ -4518,7 +4557,7 @@
       </c>
       <c r="AU5" s="24"/>
       <c r="AV5" s="24"/>
-      <c r="AW5" s="109" t="s">
+      <c r="AW5" s="111" t="s">
         <v>132</v>
       </c>
       <c r="AX5" s="26" t="s">
@@ -4531,7 +4570,7 @@
       </c>
       <c r="BB5" s="28"/>
       <c r="BC5" s="28"/>
-      <c r="BD5" s="109" t="s">
+      <c r="BD5" s="111" t="s">
         <v>135</v>
       </c>
       <c r="BE5" s="29" t="s">
@@ -4539,22 +4578,22 @@
       </c>
       <c r="BF5" s="29"/>
       <c r="BG5" s="29"/>
-      <c r="BH5" s="110" t="s">
+      <c r="BH5" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="BI5" s="111" t="s">
+      <c r="BI5" s="113" t="s">
         <v>138</v>
       </c>
-      <c r="BJ5" s="111"/>
-      <c r="BK5" s="111"/>
-      <c r="BL5" s="110" t="s">
+      <c r="BJ5" s="113"/>
+      <c r="BK5" s="113"/>
+      <c r="BL5" s="112" t="s">
         <v>139</v>
       </c>
       <c r="BM5" s="27" t="s">
         <v>140</v>
       </c>
       <c r="BN5" s="27"/>
-      <c r="BO5" s="110" t="s">
+      <c r="BO5" s="112" t="s">
         <v>141</v>
       </c>
       <c r="BP5" s="31" t="s">
@@ -4618,44 +4657,44 @@
       <c r="T6" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="112" t="n">
+      <c r="U6" s="114" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="112" t="n">
+      <c r="V6" s="114" t="n">
         <v>20</v>
       </c>
-      <c r="W6" s="112" t="n">
+      <c r="W6" s="114" t="n">
         <v>21</v>
       </c>
-      <c r="X6" s="113" t="n">
+      <c r="X6" s="115" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="113" t="n">
+      <c r="Y6" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="Z6" s="113" t="n">
+      <c r="Z6" s="115" t="n">
         <v>29</v>
       </c>
-      <c r="AA6" s="114" t="n">
+      <c r="AA6" s="116" t="n">
         <v>23</v>
       </c>
-      <c r="AB6" s="115" t="n">
+      <c r="AB6" s="117" t="n">
         <v>24</v>
       </c>
-      <c r="AC6" s="116" t="n">
+      <c r="AC6" s="118" t="n">
         <v>25</v>
       </c>
-      <c r="AD6" s="117" t="n">
+      <c r="AD6" s="119" t="n">
         <v>26</v>
       </c>
-      <c r="AE6" s="118" t="n">
+      <c r="AE6" s="120" t="n">
         <v>27</v>
       </c>
-      <c r="AF6" s="119" t="n">
+      <c r="AF6" s="121" t="n">
         <v>28</v>
       </c>
       <c r="AG6" s="20"/>
-      <c r="AH6" s="120" t="n">
+      <c r="AH6" s="122" t="n">
         <v>30</v>
       </c>
       <c r="AI6" s="48" t="n">
@@ -4673,13 +4712,13 @@
       <c r="AM6" s="49" t="n">
         <v>47</v>
       </c>
-      <c r="AN6" s="121" t="n">
+      <c r="AN6" s="123" t="n">
         <v>33</v>
       </c>
-      <c r="AO6" s="122" t="n">
+      <c r="AO6" s="124" t="n">
         <v>34</v>
       </c>
-      <c r="AP6" s="121" t="n">
+      <c r="AP6" s="123" t="n">
         <v>41</v>
       </c>
       <c r="AQ6" s="52" t="n">
@@ -4688,7 +4727,7 @@
       <c r="AR6" s="53" t="n">
         <v>49</v>
       </c>
-      <c r="AS6" s="121" t="n">
+      <c r="AS6" s="123" t="n">
         <v>36</v>
       </c>
       <c r="AT6" s="54" t="n">
@@ -4700,16 +4739,16 @@
       <c r="AV6" s="55" t="n">
         <v>52</v>
       </c>
-      <c r="AW6" s="121" t="n">
+      <c r="AW6" s="123" t="n">
         <v>37</v>
       </c>
-      <c r="AX6" s="123" t="n">
+      <c r="AX6" s="125" t="n">
         <v>53</v>
       </c>
-      <c r="AY6" s="123" t="n">
+      <c r="AY6" s="125" t="n">
         <v>54</v>
       </c>
-      <c r="AZ6" s="124" t="n">
+      <c r="AZ6" s="126" t="n">
         <v>55</v>
       </c>
       <c r="BA6" s="60" t="n">
@@ -4721,7 +4760,7 @@
       <c r="BC6" s="62" t="n">
         <v>58</v>
       </c>
-      <c r="BD6" s="121" t="n">
+      <c r="BD6" s="123" t="n">
         <v>137</v>
       </c>
       <c r="BE6" s="63" t="n">
@@ -4733,19 +4772,19 @@
       <c r="BG6" s="65" t="n">
         <v>61</v>
       </c>
-      <c r="BH6" s="122" t="n">
+      <c r="BH6" s="124" t="n">
         <v>138</v>
       </c>
-      <c r="BI6" s="125" t="n">
+      <c r="BI6" s="127" t="n">
         <v>62</v>
       </c>
-      <c r="BJ6" s="126" t="n">
+      <c r="BJ6" s="128" t="n">
         <v>63</v>
       </c>
-      <c r="BK6" s="127" t="n">
+      <c r="BK6" s="129" t="n">
         <v>64</v>
       </c>
-      <c r="BL6" s="122" t="n">
+      <c r="BL6" s="124" t="n">
         <v>139</v>
       </c>
       <c r="BM6" s="58" t="n">
@@ -4754,7 +4793,7 @@
       <c r="BN6" s="59" t="n">
         <v>66</v>
       </c>
-      <c r="BO6" s="122" t="n">
+      <c r="BO6" s="124" t="n">
         <v>38</v>
       </c>
       <c r="BP6" s="31"/>
@@ -4797,331 +4836,331 @@
         <v>144</v>
       </c>
       <c r="T7" s="71"/>
-      <c r="U7" s="128" t="s">
+      <c r="U7" s="130" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="128"/>
-      <c r="W7" s="129" t="s">
+      <c r="V7" s="130"/>
+      <c r="W7" s="131" t="s">
         <v>146</v>
       </c>
-      <c r="X7" s="130" t="s">
+      <c r="X7" s="132" t="s">
         <v>147</v>
       </c>
-      <c r="Y7" s="131" t="s">
+      <c r="Y7" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="Z7" s="131" t="s">
+      <c r="Z7" s="133" t="s">
         <v>149</v>
       </c>
-      <c r="AA7" s="132" t="s">
+      <c r="AA7" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="133" t="s">
+      <c r="AB7" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="AC7" s="134" t="s">
+      <c r="AC7" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="135" t="s">
+      <c r="AD7" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="136" t="s">
+      <c r="AE7" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="137" t="s">
+      <c r="AF7" s="139" t="s">
         <v>41</v>
       </c>
       <c r="AG7" s="20"/>
-      <c r="AH7" s="138" t="s">
+      <c r="AH7" s="140" t="s">
         <v>42</v>
       </c>
-      <c r="AI7" s="139" t="s">
+      <c r="AI7" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="AJ7" s="138" t="s">
+      <c r="AJ7" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="AK7" s="140" t="s">
+      <c r="AK7" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="AL7" s="141" t="s">
+      <c r="AL7" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="AM7" s="142" t="s">
+      <c r="AM7" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="AN7" s="143" t="s">
+      <c r="AN7" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="144" t="s">
+      <c r="AO7" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="AP7" s="145"/>
-      <c r="AQ7" s="146" t="s">
+      <c r="AP7" s="147"/>
+      <c r="AQ7" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="AR7" s="147" t="s">
+      <c r="AR7" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="AS7" s="145"/>
-      <c r="AT7" s="148" t="n">
+      <c r="AS7" s="147"/>
+      <c r="AT7" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" s="149" t="n">
+      <c r="AU7" s="151" t="n">
         <v>-1</v>
       </c>
-      <c r="AV7" s="150" t="n">
+      <c r="AV7" s="152" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AW7" s="151"/>
-      <c r="AX7" s="152" t="n">
+      <c r="AW7" s="153"/>
+      <c r="AX7" s="154" t="n">
         <v>0</v>
       </c>
       <c r="AY7" s="57" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ7" s="153" t="n">
+      <c r="AZ7" s="155" t="n">
         <v>-1.5</v>
       </c>
-      <c r="BA7" s="154" t="s">
+      <c r="BA7" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="BB7" s="155" t="s">
+      <c r="BB7" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="BC7" s="156" t="s">
+      <c r="BC7" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="BD7" s="151"/>
-      <c r="BE7" s="157" t="s">
+      <c r="BD7" s="153"/>
+      <c r="BE7" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="BF7" s="158" t="s">
+      <c r="BF7" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="BG7" s="159" t="s">
+      <c r="BG7" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="BH7" s="151"/>
-      <c r="BI7" s="160" t="s">
+      <c r="BH7" s="153"/>
+      <c r="BI7" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="BJ7" s="161" t="s">
+      <c r="BJ7" s="163" t="s">
         <v>43</v>
       </c>
-      <c r="BK7" s="162" t="s">
+      <c r="BK7" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="BL7" s="151"/>
-      <c r="BM7" s="163" t="s">
+      <c r="BL7" s="153"/>
+      <c r="BM7" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="BN7" s="164" t="s">
+      <c r="BN7" s="166" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="165"/>
+      <c r="BO7" s="167"/>
       <c r="BP7" s="31"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="102" t="s">
+      <c r="G8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="102" t="s">
+      <c r="H8" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="102" t="s">
+      <c r="I8" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="102" t="s">
+      <c r="J8" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="102" t="s">
+      <c r="K8" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="102" t="s">
+      <c r="L8" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="102" t="s">
+      <c r="M8" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="102" t="s">
+      <c r="N8" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="102" t="s">
+      <c r="O8" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="102" t="s">
+      <c r="P8" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="102" t="s">
+      <c r="Q8" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="102" t="s">
+      <c r="R8" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="102" t="s">
+      <c r="S8" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="T8" s="102" t="s">
+      <c r="T8" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="102" t="s">
+      <c r="U8" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="102" t="s">
+      <c r="V8" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="102" t="s">
+      <c r="W8" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="102" t="s">
+      <c r="X8" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="102" t="s">
+      <c r="Y8" s="101" t="s">
         <v>151</v>
       </c>
-      <c r="Z8" s="102" t="s">
+      <c r="Z8" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="AA8" s="102" t="s">
+      <c r="AA8" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="AB8" s="102" t="s">
+      <c r="AB8" s="101" t="s">
         <v>152</v>
       </c>
-      <c r="AC8" s="102" t="s">
+      <c r="AC8" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="AD8" s="102" t="s">
+      <c r="AD8" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="AE8" s="102" t="s">
+      <c r="AE8" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AF8" s="102" t="s">
+      <c r="AF8" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="102" t="s">
+      <c r="AG8" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="AH8" s="102" t="s">
+      <c r="AH8" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="102" t="s">
+      <c r="AI8" s="101" t="s">
         <v>153</v>
       </c>
-      <c r="AJ8" s="102" t="s">
+      <c r="AJ8" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="AK8" s="102" t="s">
+      <c r="AK8" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="AL8" s="102" t="s">
+      <c r="AL8" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="AM8" s="102" t="s">
+      <c r="AM8" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="AN8" s="102" t="s">
+      <c r="AN8" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="AO8" s="102" t="s">
+      <c r="AO8" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="AP8" s="102" t="s">
+      <c r="AP8" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="AQ8" s="102" t="s">
+      <c r="AQ8" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="AR8" s="102" t="s">
+      <c r="AR8" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="AS8" s="102" t="s">
+      <c r="AS8" s="101" t="s">
         <v>96</v>
       </c>
-      <c r="AT8" s="102" t="s">
+      <c r="AT8" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="AU8" s="102" t="s">
+      <c r="AU8" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="AV8" s="102" t="s">
+      <c r="AV8" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="AW8" s="102" t="s">
+      <c r="AW8" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="AX8" s="102" t="s">
+      <c r="AX8" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="AY8" s="102" t="s">
+      <c r="AY8" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="AZ8" s="102" t="s">
+      <c r="AZ8" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="BA8" s="102" t="s">
+      <c r="BA8" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="BB8" s="102" t="s">
+      <c r="BB8" s="101" t="s">
         <v>122</v>
       </c>
-      <c r="BC8" s="102" t="s">
+      <c r="BC8" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="BD8" s="102" t="s">
+      <c r="BD8" s="101" t="s">
         <v>155</v>
       </c>
-      <c r="BE8" s="102" t="s">
+      <c r="BE8" s="101" t="s">
         <v>156</v>
       </c>
-      <c r="BF8" s="102" t="s">
+      <c r="BF8" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="BG8" s="102" t="s">
+      <c r="BG8" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="BH8" s="102" t="s">
+      <c r="BH8" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="BI8" s="102" t="s">
+      <c r="BI8" s="101" t="s">
         <v>160</v>
       </c>
-      <c r="BJ8" s="102" t="s">
+      <c r="BJ8" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="BK8" s="102" t="s">
+      <c r="BK8" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="BL8" s="102" t="s">
+      <c r="BL8" s="101" t="s">
         <v>163</v>
       </c>
-      <c r="BM8" s="102" t="s">
+      <c r="BM8" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="BN8" s="102" t="s">
+      <c r="BN8" s="101" t="s">
         <v>165</v>
       </c>
-      <c r="BO8" s="102" t="s">
+      <c r="BO8" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="BP8" s="102" t="s">
+      <c r="BP8" s="101" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5174,12 +5213,27 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BP9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="100.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="50" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="56" min="56" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="57" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="60" min="60" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="61" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="64" min="64" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="65" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="67" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="100.67"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5272,28 +5326,28 @@
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
-      <c r="U5" s="104" t="s">
+      <c r="U5" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="V5" s="104"/>
-      <c r="W5" s="104"/>
-      <c r="X5" s="105" t="s">
+      <c r="V5" s="106"/>
+      <c r="W5" s="106"/>
+      <c r="X5" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
+      <c r="Y5" s="107"/>
+      <c r="Z5" s="107"/>
       <c r="AA5" s="18" t="s">
         <v>11</v>
       </c>
       <c r="AB5" s="18"/>
-      <c r="AC5" s="106" t="s">
+      <c r="AC5" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="AD5" s="106"/>
-      <c r="AE5" s="107" t="s">
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="AF5" s="107"/>
+      <c r="AF5" s="109"/>
       <c r="AG5" s="20" t="s">
         <v>14</v>
       </c>
@@ -5307,18 +5361,18 @@
       </c>
       <c r="AL5" s="22"/>
       <c r="AM5" s="22"/>
-      <c r="AN5" s="108" t="s">
+      <c r="AN5" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="AO5" s="108"/>
-      <c r="AP5" s="108" t="s">
+      <c r="AO5" s="110"/>
+      <c r="AP5" s="110" t="s">
         <v>18</v>
       </c>
       <c r="AQ5" s="23" t="s">
         <v>129</v>
       </c>
       <c r="AR5" s="23"/>
-      <c r="AS5" s="109" t="s">
+      <c r="AS5" s="111" t="s">
         <v>130</v>
       </c>
       <c r="AT5" s="24" t="s">
@@ -5326,7 +5380,7 @@
       </c>
       <c r="AU5" s="24"/>
       <c r="AV5" s="24"/>
-      <c r="AW5" s="109" t="s">
+      <c r="AW5" s="111" t="s">
         <v>132</v>
       </c>
       <c r="AX5" s="26" t="s">
@@ -5339,7 +5393,7 @@
       </c>
       <c r="BB5" s="28"/>
       <c r="BC5" s="28"/>
-      <c r="BD5" s="109" t="s">
+      <c r="BD5" s="111" t="s">
         <v>135</v>
       </c>
       <c r="BE5" s="29" t="s">
@@ -5347,22 +5401,22 @@
       </c>
       <c r="BF5" s="29"/>
       <c r="BG5" s="29"/>
-      <c r="BH5" s="110" t="s">
+      <c r="BH5" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="BI5" s="111" t="s">
+      <c r="BI5" s="113" t="s">
         <v>138</v>
       </c>
-      <c r="BJ5" s="111"/>
-      <c r="BK5" s="111"/>
-      <c r="BL5" s="110" t="s">
+      <c r="BJ5" s="113"/>
+      <c r="BK5" s="113"/>
+      <c r="BL5" s="112" t="s">
         <v>139</v>
       </c>
       <c r="BM5" s="27" t="s">
         <v>140</v>
       </c>
       <c r="BN5" s="27"/>
-      <c r="BO5" s="110" t="s">
+      <c r="BO5" s="112" t="s">
         <v>141</v>
       </c>
       <c r="BP5" s="31" t="s">
@@ -5426,44 +5480,44 @@
       <c r="T6" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="112" t="n">
+      <c r="U6" s="114" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="112" t="n">
+      <c r="V6" s="114" t="n">
         <v>20</v>
       </c>
-      <c r="W6" s="112" t="n">
+      <c r="W6" s="114" t="n">
         <v>21</v>
       </c>
-      <c r="X6" s="113" t="n">
+      <c r="X6" s="115" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="113" t="n">
+      <c r="Y6" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="Z6" s="113" t="n">
+      <c r="Z6" s="115" t="n">
         <v>29</v>
       </c>
-      <c r="AA6" s="114" t="n">
+      <c r="AA6" s="116" t="n">
         <v>23</v>
       </c>
-      <c r="AB6" s="115" t="n">
+      <c r="AB6" s="117" t="n">
         <v>24</v>
       </c>
-      <c r="AC6" s="116" t="n">
+      <c r="AC6" s="118" t="n">
         <v>25</v>
       </c>
-      <c r="AD6" s="117" t="n">
+      <c r="AD6" s="119" t="n">
         <v>26</v>
       </c>
-      <c r="AE6" s="118" t="n">
+      <c r="AE6" s="120" t="n">
         <v>27</v>
       </c>
-      <c r="AF6" s="119" t="n">
+      <c r="AF6" s="121" t="n">
         <v>28</v>
       </c>
       <c r="AG6" s="20"/>
-      <c r="AH6" s="120" t="n">
+      <c r="AH6" s="122" t="n">
         <v>30</v>
       </c>
       <c r="AI6" s="48" t="n">
@@ -5481,13 +5535,13 @@
       <c r="AM6" s="49" t="n">
         <v>47</v>
       </c>
-      <c r="AN6" s="121" t="n">
+      <c r="AN6" s="123" t="n">
         <v>33</v>
       </c>
-      <c r="AO6" s="122" t="n">
+      <c r="AO6" s="124" t="n">
         <v>34</v>
       </c>
-      <c r="AP6" s="121" t="n">
+      <c r="AP6" s="123" t="n">
         <v>41</v>
       </c>
       <c r="AQ6" s="52" t="n">
@@ -5496,7 +5550,7 @@
       <c r="AR6" s="53" t="n">
         <v>49</v>
       </c>
-      <c r="AS6" s="121" t="n">
+      <c r="AS6" s="123" t="n">
         <v>36</v>
       </c>
       <c r="AT6" s="54" t="n">
@@ -5508,16 +5562,16 @@
       <c r="AV6" s="55" t="n">
         <v>52</v>
       </c>
-      <c r="AW6" s="121" t="n">
+      <c r="AW6" s="123" t="n">
         <v>37</v>
       </c>
-      <c r="AX6" s="123" t="n">
+      <c r="AX6" s="125" t="n">
         <v>53</v>
       </c>
-      <c r="AY6" s="123" t="n">
+      <c r="AY6" s="125" t="n">
         <v>54</v>
       </c>
-      <c r="AZ6" s="124" t="n">
+      <c r="AZ6" s="126" t="n">
         <v>55</v>
       </c>
       <c r="BA6" s="60" t="n">
@@ -5529,7 +5583,7 @@
       <c r="BC6" s="62" t="n">
         <v>58</v>
       </c>
-      <c r="BD6" s="121" t="n">
+      <c r="BD6" s="123" t="n">
         <v>137</v>
       </c>
       <c r="BE6" s="63" t="n">
@@ -5541,19 +5595,19 @@
       <c r="BG6" s="65" t="n">
         <v>61</v>
       </c>
-      <c r="BH6" s="122" t="n">
+      <c r="BH6" s="124" t="n">
         <v>138</v>
       </c>
-      <c r="BI6" s="125" t="n">
+      <c r="BI6" s="127" t="n">
         <v>62</v>
       </c>
-      <c r="BJ6" s="126" t="n">
+      <c r="BJ6" s="128" t="n">
         <v>63</v>
       </c>
-      <c r="BK6" s="127" t="n">
+      <c r="BK6" s="129" t="n">
         <v>64</v>
       </c>
-      <c r="BL6" s="122" t="n">
+      <c r="BL6" s="124" t="n">
         <v>139</v>
       </c>
       <c r="BM6" s="58" t="n">
@@ -5562,7 +5616,7 @@
       <c r="BN6" s="59" t="n">
         <v>66</v>
       </c>
-      <c r="BO6" s="122" t="n">
+      <c r="BO6" s="124" t="n">
         <v>38</v>
       </c>
       <c r="BP6" s="31"/>
@@ -5605,332 +5659,332 @@
         <v>144</v>
       </c>
       <c r="T7" s="71"/>
-      <c r="U7" s="128" t="s">
+      <c r="U7" s="130" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="128"/>
-      <c r="W7" s="129" t="s">
+      <c r="V7" s="130"/>
+      <c r="W7" s="131" t="s">
         <v>146</v>
       </c>
-      <c r="X7" s="130" t="s">
+      <c r="X7" s="132" t="s">
         <v>147</v>
       </c>
-      <c r="Y7" s="131" t="s">
+      <c r="Y7" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="Z7" s="131" t="s">
+      <c r="Z7" s="133" t="s">
         <v>149</v>
       </c>
-      <c r="AA7" s="132" t="s">
+      <c r="AA7" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="133" t="s">
+      <c r="AB7" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="AC7" s="134" t="s">
+      <c r="AC7" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="135" t="s">
+      <c r="AD7" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="136" t="s">
+      <c r="AE7" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="137" t="s">
+      <c r="AF7" s="139" t="s">
         <v>41</v>
       </c>
       <c r="AG7" s="20"/>
-      <c r="AH7" s="138" t="s">
+      <c r="AH7" s="140" t="s">
         <v>42</v>
       </c>
-      <c r="AI7" s="139" t="s">
+      <c r="AI7" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="AJ7" s="138" t="s">
+      <c r="AJ7" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="AK7" s="140" t="s">
+      <c r="AK7" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="AL7" s="141" t="s">
+      <c r="AL7" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="AM7" s="142" t="s">
+      <c r="AM7" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="AN7" s="143" t="s">
+      <c r="AN7" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="144" t="s">
+      <c r="AO7" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="AP7" s="145"/>
-      <c r="AQ7" s="146" t="s">
+      <c r="AP7" s="147"/>
+      <c r="AQ7" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="AR7" s="147" t="s">
+      <c r="AR7" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="AS7" s="145"/>
-      <c r="AT7" s="148" t="n">
+      <c r="AS7" s="147"/>
+      <c r="AT7" s="150" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" s="149" t="n">
+      <c r="AU7" s="151" t="n">
         <v>-1</v>
       </c>
-      <c r="AV7" s="150" t="n">
+      <c r="AV7" s="152" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AW7" s="151"/>
-      <c r="AX7" s="152" t="n">
+      <c r="AW7" s="153"/>
+      <c r="AX7" s="154" t="n">
         <v>0</v>
       </c>
       <c r="AY7" s="57" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ7" s="153" t="n">
+      <c r="AZ7" s="155" t="n">
         <v>-1.5</v>
       </c>
-      <c r="BA7" s="154" t="s">
+      <c r="BA7" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="BB7" s="155" t="s">
+      <c r="BB7" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="BC7" s="156" t="s">
+      <c r="BC7" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="BD7" s="151"/>
-      <c r="BE7" s="157" t="s">
+      <c r="BD7" s="153"/>
+      <c r="BE7" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="BF7" s="158" t="s">
+      <c r="BF7" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="BG7" s="159" t="s">
+      <c r="BG7" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="BH7" s="151"/>
-      <c r="BI7" s="160" t="s">
+      <c r="BH7" s="153"/>
+      <c r="BI7" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="BJ7" s="161" t="s">
+      <c r="BJ7" s="163" t="s">
         <v>43</v>
       </c>
-      <c r="BK7" s="162" t="s">
+      <c r="BK7" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="BL7" s="151"/>
-      <c r="BM7" s="163" t="s">
+      <c r="BL7" s="153"/>
+      <c r="BM7" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="BN7" s="164" t="s">
+      <c r="BN7" s="166" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="165"/>
+      <c r="BO7" s="167"/>
       <c r="BP7" s="31"/>
     </row>
-    <row r="8" s="103" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="105" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="102" t="s">
+      <c r="G8" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="102" t="s">
+      <c r="H8" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="102" t="s">
+      <c r="I8" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="102" t="s">
+      <c r="J8" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="102" t="s">
+      <c r="K8" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="102" t="s">
+      <c r="L8" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="102" t="s">
+      <c r="M8" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="102" t="s">
+      <c r="N8" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="102" t="s">
+      <c r="O8" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="102" t="s">
+      <c r="P8" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="102" t="s">
+      <c r="Q8" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="102" t="s">
+      <c r="R8" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="102" t="s">
+      <c r="S8" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="T8" s="102" t="s">
+      <c r="T8" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="102" t="s">
+      <c r="U8" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="102" t="s">
+      <c r="V8" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="102" t="s">
+      <c r="W8" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="102" t="s">
+      <c r="X8" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="102" t="s">
+      <c r="Y8" s="101" t="s">
         <v>151</v>
       </c>
-      <c r="Z8" s="102" t="s">
+      <c r="Z8" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="AA8" s="102" t="s">
+      <c r="AA8" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="AB8" s="102" t="s">
+      <c r="AB8" s="101" t="s">
         <v>152</v>
       </c>
-      <c r="AC8" s="102" t="s">
+      <c r="AC8" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="AD8" s="102" t="s">
+      <c r="AD8" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="AE8" s="102" t="s">
+      <c r="AE8" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AF8" s="102" t="s">
+      <c r="AF8" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="102" t="s">
+      <c r="AG8" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="AH8" s="102" t="s">
+      <c r="AH8" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="102" t="s">
+      <c r="AI8" s="101" t="s">
         <v>153</v>
       </c>
-      <c r="AJ8" s="102" t="s">
+      <c r="AJ8" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="AK8" s="102" t="s">
+      <c r="AK8" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="AL8" s="102" t="s">
+      <c r="AL8" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="AM8" s="102" t="s">
+      <c r="AM8" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="AN8" s="102" t="s">
+      <c r="AN8" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="AO8" s="102" t="s">
+      <c r="AO8" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="AP8" s="102" t="s">
+      <c r="AP8" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="AQ8" s="102" t="s">
+      <c r="AQ8" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="AR8" s="102" t="s">
+      <c r="AR8" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="AS8" s="102" t="s">
+      <c r="AS8" s="101" t="s">
         <v>96</v>
       </c>
-      <c r="AT8" s="102" t="s">
+      <c r="AT8" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="AU8" s="102" t="s">
+      <c r="AU8" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="AV8" s="102" t="s">
+      <c r="AV8" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="AW8" s="102" t="s">
+      <c r="AW8" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="AX8" s="102" t="s">
+      <c r="AX8" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="AY8" s="102" t="s">
+      <c r="AY8" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="AZ8" s="102" t="s">
+      <c r="AZ8" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="BA8" s="102" t="s">
+      <c r="BA8" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="BB8" s="102" t="s">
+      <c r="BB8" s="101" t="s">
         <v>122</v>
       </c>
-      <c r="BC8" s="102" t="s">
+      <c r="BC8" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="BD8" s="102" t="s">
+      <c r="BD8" s="101" t="s">
         <v>155</v>
       </c>
-      <c r="BE8" s="102" t="s">
+      <c r="BE8" s="101" t="s">
         <v>156</v>
       </c>
-      <c r="BF8" s="102" t="s">
+      <c r="BF8" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="BG8" s="102" t="s">
+      <c r="BG8" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="BH8" s="102" t="s">
+      <c r="BH8" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="BI8" s="102" t="s">
+      <c r="BI8" s="101" t="s">
         <v>160</v>
       </c>
-      <c r="BJ8" s="102" t="s">
+      <c r="BJ8" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="BK8" s="102" t="s">
+      <c r="BK8" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="BL8" s="102" t="s">
+      <c r="BL8" s="101" t="s">
         <v>163</v>
       </c>
-      <c r="BM8" s="102" t="s">
+      <c r="BM8" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="BN8" s="102" t="s">
+      <c r="BN8" s="101" t="s">
         <v>165</v>
       </c>
-      <c r="BO8" s="102" t="s">
+      <c r="BO8" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="BP8" s="102" t="s">
+      <c r="BP8" s="101" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6051,13 +6105,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN8"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="0" width="100.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="22" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="26" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="32" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="38" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="39" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="55" min="55" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="56" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="0" width="100.67"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6119,62 +6183,62 @@
       <c r="G5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="166" t="s">
+      <c r="H5" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="167" t="s">
+      <c r="I5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="166" t="s">
+      <c r="J5" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="168" t="s">
+      <c r="K5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="168"/>
-      <c r="M5" s="169" t="s">
+      <c r="L5" s="169"/>
+      <c r="M5" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="169"/>
-      <c r="Q5" s="169"/>
-      <c r="R5" s="169"/>
-      <c r="S5" s="170" t="s">
+      <c r="N5" s="170"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="170"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="170"/>
+      <c r="S5" s="171" t="s">
         <v>166</v>
       </c>
-      <c r="T5" s="170"/>
-      <c r="U5" s="170"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
       <c r="V5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="171" t="s">
+      <c r="W5" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="171"/>
-      <c r="Y5" s="171"/>
-      <c r="Z5" s="172" t="s">
+      <c r="X5" s="172"/>
+      <c r="Y5" s="172"/>
+      <c r="Z5" s="173" t="s">
         <v>17</v>
       </c>
-      <c r="AA5" s="172"/>
-      <c r="AB5" s="173" t="s">
+      <c r="AA5" s="173"/>
+      <c r="AB5" s="174" t="s">
         <v>18</v>
       </c>
-      <c r="AC5" s="171" t="s">
+      <c r="AC5" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="AD5" s="171"/>
+      <c r="AD5" s="172"/>
       <c r="AE5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="174" t="s">
+      <c r="AF5" s="175" t="s">
         <v>167</v>
       </c>
-      <c r="AG5" s="174"/>
-      <c r="AH5" s="174"/>
-      <c r="AI5" s="174"/>
-      <c r="AJ5" s="174"/>
-      <c r="AK5" s="174"/>
+      <c r="AG5" s="175"/>
+      <c r="AH5" s="175"/>
+      <c r="AI5" s="175"/>
+      <c r="AJ5" s="175"/>
+      <c r="AK5" s="175"/>
       <c r="AL5" s="18" t="s">
         <v>168</v>
       </c>
@@ -6184,46 +6248,46 @@
       <c r="AN5" s="14"/>
       <c r="AO5" s="14"/>
       <c r="AP5" s="14"/>
-      <c r="AQ5" s="174" t="s">
+      <c r="AQ5" s="175" t="s">
         <v>170</v>
       </c>
-      <c r="AR5" s="174"/>
-      <c r="AS5" s="174"/>
-      <c r="AT5" s="174"/>
+      <c r="AR5" s="175"/>
+      <c r="AS5" s="175"/>
+      <c r="AT5" s="175"/>
       <c r="AU5" s="14" t="s">
         <v>171</v>
       </c>
       <c r="AV5" s="14"/>
       <c r="AW5" s="14"/>
       <c r="AX5" s="14"/>
-      <c r="AY5" s="174" t="s">
+      <c r="AY5" s="175" t="s">
         <v>172</v>
       </c>
-      <c r="AZ5" s="174"/>
-      <c r="BA5" s="174"/>
-      <c r="BB5" s="174"/>
+      <c r="AZ5" s="175"/>
+      <c r="BA5" s="175"/>
+      <c r="BB5" s="175"/>
       <c r="BC5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="BD5" s="108" t="s">
+      <c r="BD5" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="BE5" s="108"/>
-      <c r="BF5" s="108"/>
-      <c r="BG5" s="108"/>
-      <c r="BH5" s="175" t="s">
+      <c r="BE5" s="110"/>
+      <c r="BF5" s="110"/>
+      <c r="BG5" s="110"/>
+      <c r="BH5" s="176" t="s">
         <v>173</v>
       </c>
-      <c r="BI5" s="175"/>
-      <c r="BJ5" s="108" t="s">
+      <c r="BI5" s="176"/>
+      <c r="BJ5" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="BK5" s="108"/>
-      <c r="BL5" s="175" t="s">
+      <c r="BK5" s="110"/>
+      <c r="BL5" s="176" t="s">
         <v>175</v>
       </c>
-      <c r="BM5" s="175"/>
-      <c r="BN5" s="176" t="s">
+      <c r="BM5" s="176"/>
+      <c r="BN5" s="177" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6245,19 +6309,19 @@
       <c r="G6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="167" t="n">
+      <c r="H6" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="167" t="n">
+      <c r="I6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="167" t="n">
+      <c r="J6" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="177" t="n">
+      <c r="K6" s="178" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="177" t="n">
+      <c r="L6" s="178" t="n">
         <v>10</v>
       </c>
       <c r="M6" s="41" t="n">
@@ -6278,26 +6342,26 @@
       <c r="R6" s="41" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="178" t="n">
+      <c r="S6" s="179" t="n">
         <v>76</v>
       </c>
-      <c r="T6" s="178" t="n">
+      <c r="T6" s="179" t="n">
         <v>77</v>
       </c>
-      <c r="U6" s="179" t="n">
+      <c r="U6" s="180" t="n">
         <v>78</v>
       </c>
       <c r="V6" s="20"/>
-      <c r="W6" s="180" t="n">
+      <c r="W6" s="181" t="n">
         <v>32</v>
       </c>
-      <c r="X6" s="180" t="n">
+      <c r="X6" s="181" t="n">
         <v>33</v>
       </c>
-      <c r="Y6" s="180" t="n">
+      <c r="Y6" s="181" t="n">
         <v>34</v>
       </c>
-      <c r="Z6" s="181" t="n">
+      <c r="Z6" s="182" t="n">
         <v>28</v>
       </c>
       <c r="AA6" s="18" t="n">
@@ -6306,118 +6370,118 @@
       <c r="AB6" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="AC6" s="180" t="n">
+      <c r="AC6" s="181" t="n">
         <v>38</v>
       </c>
-      <c r="AD6" s="180" t="n">
+      <c r="AD6" s="181" t="n">
         <v>39</v>
       </c>
       <c r="AE6" s="18" t="n">
         <v>127</v>
       </c>
-      <c r="AF6" s="182" t="n">
+      <c r="AF6" s="183" t="n">
         <v>91</v>
       </c>
-      <c r="AG6" s="183" t="n">
+      <c r="AG6" s="184" t="n">
         <v>92</v>
       </c>
-      <c r="AH6" s="184" t="n">
+      <c r="AH6" s="185" t="n">
         <v>93</v>
       </c>
-      <c r="AI6" s="185" t="n">
+      <c r="AI6" s="186" t="n">
         <v>94</v>
       </c>
-      <c r="AJ6" s="185" t="n">
+      <c r="AJ6" s="186" t="n">
         <v>95</v>
       </c>
-      <c r="AK6" s="185" t="n">
+      <c r="AK6" s="186" t="n">
         <v>96</v>
       </c>
-      <c r="AL6" s="186" t="n">
+      <c r="AL6" s="187" t="n">
         <v>129</v>
       </c>
-      <c r="AM6" s="187" t="n">
+      <c r="AM6" s="188" t="n">
         <v>97</v>
       </c>
-      <c r="AN6" s="187" t="n">
+      <c r="AN6" s="188" t="n">
         <v>98</v>
       </c>
-      <c r="AO6" s="185" t="n">
+      <c r="AO6" s="186" t="n">
         <v>99</v>
       </c>
-      <c r="AP6" s="185" t="n">
+      <c r="AP6" s="186" t="n">
         <v>100</v>
       </c>
-      <c r="AQ6" s="184" t="n">
+      <c r="AQ6" s="185" t="n">
         <v>101</v>
       </c>
-      <c r="AR6" s="184" t="n">
+      <c r="AR6" s="185" t="n">
         <v>102</v>
       </c>
-      <c r="AS6" s="185" t="n">
+      <c r="AS6" s="186" t="n">
         <v>103</v>
       </c>
-      <c r="AT6" s="185" t="n">
+      <c r="AT6" s="186" t="n">
         <v>104</v>
       </c>
-      <c r="AU6" s="187" t="n">
+      <c r="AU6" s="188" t="n">
         <v>105</v>
       </c>
-      <c r="AV6" s="187" t="n">
+      <c r="AV6" s="188" t="n">
         <v>106</v>
       </c>
-      <c r="AW6" s="185" t="n">
+      <c r="AW6" s="186" t="n">
         <v>107</v>
       </c>
-      <c r="AX6" s="185" t="n">
+      <c r="AX6" s="186" t="n">
         <v>108</v>
       </c>
-      <c r="AY6" s="184" t="n">
+      <c r="AY6" s="185" t="n">
         <v>109</v>
       </c>
-      <c r="AZ6" s="184" t="n">
+      <c r="AZ6" s="185" t="n">
         <v>110</v>
       </c>
-      <c r="BA6" s="185" t="n">
+      <c r="BA6" s="186" t="n">
         <v>111</v>
       </c>
-      <c r="BB6" s="185" t="n">
+      <c r="BB6" s="186" t="n">
         <v>112</v>
       </c>
       <c r="BC6" s="18" t="n">
         <v>128</v>
       </c>
-      <c r="BD6" s="188" t="n">
+      <c r="BD6" s="189" t="n">
         <v>113</v>
       </c>
-      <c r="BE6" s="188" t="n">
+      <c r="BE6" s="189" t="n">
         <v>114</v>
       </c>
-      <c r="BF6" s="165" t="n">
+      <c r="BF6" s="167" t="n">
         <v>115</v>
       </c>
-      <c r="BG6" s="165" t="n">
+      <c r="BG6" s="167" t="n">
         <v>116</v>
       </c>
-      <c r="BH6" s="188" t="n">
+      <c r="BH6" s="189" t="n">
         <v>117</v>
       </c>
-      <c r="BI6" s="188" t="n">
+      <c r="BI6" s="189" t="n">
         <v>118</v>
       </c>
-      <c r="BJ6" s="165" t="n">
+      <c r="BJ6" s="167" t="n">
         <v>119</v>
       </c>
-      <c r="BK6" s="165" t="n">
+      <c r="BK6" s="167" t="n">
         <v>120</v>
       </c>
-      <c r="BL6" s="188" t="n">
+      <c r="BL6" s="189" t="n">
         <v>121</v>
       </c>
-      <c r="BM6" s="188" t="n">
+      <c r="BM6" s="189" t="n">
         <v>122</v>
       </c>
-      <c r="BN6" s="176"/>
+      <c r="BN6" s="177"/>
     </row>
     <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="10"/>
@@ -6432,13 +6496,13 @@
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="167"/>
-      <c r="I7" s="166"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="177" t="s">
+      <c r="H7" s="30"/>
+      <c r="I7" s="168"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="178" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="189" t="s">
+      <c r="L7" s="190" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="16" t="s">
@@ -6449,27 +6513,27 @@
         <v>38</v>
       </c>
       <c r="P7" s="70"/>
-      <c r="Q7" s="190" t="s">
+      <c r="Q7" s="191" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="190"/>
-      <c r="S7" s="191" t="s">
+      <c r="R7" s="191"/>
+      <c r="S7" s="192" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="192" t="s">
+      <c r="T7" s="193" t="s">
         <v>176</v>
       </c>
-      <c r="U7" s="193" t="s">
+      <c r="U7" s="194" t="s">
         <v>177</v>
       </c>
       <c r="V7" s="20"/>
-      <c r="W7" s="194" t="s">
+      <c r="W7" s="195" t="s">
         <v>42</v>
       </c>
-      <c r="X7" s="195" t="s">
+      <c r="X7" s="196" t="s">
         <v>43</v>
       </c>
-      <c r="Y7" s="196" t="s">
+      <c r="Y7" s="197" t="s">
         <v>44</v>
       </c>
       <c r="Z7" s="74" t="s">
@@ -6478,378 +6542,310 @@
       <c r="AA7" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="AB7" s="197"/>
-      <c r="AC7" s="198" t="s">
+      <c r="AB7" s="198"/>
+      <c r="AC7" s="199" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="199" t="s">
+      <c r="AD7" s="200" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="197"/>
-      <c r="AF7" s="200" t="s">
+      <c r="AE7" s="198"/>
+      <c r="AF7" s="201" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="201" t="s">
+      <c r="AG7" s="202" t="s">
         <v>179</v>
       </c>
-      <c r="AH7" s="202" t="s">
+      <c r="AH7" s="203" t="s">
         <v>180</v>
       </c>
-      <c r="AI7" s="203" t="s">
+      <c r="AI7" s="204" t="s">
         <v>181</v>
       </c>
-      <c r="AJ7" s="204" t="s">
+      <c r="AJ7" s="205" t="s">
         <v>182</v>
       </c>
-      <c r="AK7" s="205" t="s">
+      <c r="AK7" s="206" t="s">
         <v>183</v>
       </c>
-      <c r="AL7" s="206"/>
+      <c r="AL7" s="207"/>
       <c r="AM7" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="AN7" s="100" t="s">
+      <c r="AN7" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="AO7" s="204" t="s">
+      <c r="AO7" s="205" t="s">
         <v>185</v>
       </c>
-      <c r="AP7" s="207" t="s">
+      <c r="AP7" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="AQ7" s="208" t="s">
+      <c r="AQ7" s="209" t="s">
         <v>184</v>
       </c>
-      <c r="AR7" s="209" t="s">
+      <c r="AR7" s="210" t="s">
         <v>178</v>
       </c>
-      <c r="AS7" s="204" t="s">
+      <c r="AS7" s="205" t="s">
         <v>185</v>
       </c>
-      <c r="AT7" s="207" t="s">
+      <c r="AT7" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="AU7" s="210" t="s">
+      <c r="AU7" s="211" t="s">
         <v>186</v>
       </c>
-      <c r="AV7" s="211" t="s">
+      <c r="AV7" s="212" t="s">
         <v>178</v>
       </c>
-      <c r="AW7" s="204" t="s">
+      <c r="AW7" s="205" t="s">
         <v>187</v>
       </c>
-      <c r="AX7" s="207" t="s">
+      <c r="AX7" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="AY7" s="208" t="s">
+      <c r="AY7" s="209" t="s">
         <v>186</v>
       </c>
-      <c r="AZ7" s="209" t="s">
+      <c r="AZ7" s="210" t="s">
         <v>178</v>
       </c>
-      <c r="BA7" s="204" t="s">
+      <c r="BA7" s="205" t="s">
         <v>187</v>
       </c>
-      <c r="BB7" s="207" t="s">
+      <c r="BB7" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="BC7" s="197"/>
-      <c r="BD7" s="212" t="s">
+      <c r="BC7" s="198"/>
+      <c r="BD7" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="BE7" s="213" t="s">
+      <c r="BE7" s="214" t="s">
         <v>50</v>
       </c>
-      <c r="BF7" s="214" t="s">
+      <c r="BF7" s="215" t="s">
         <v>188</v>
       </c>
-      <c r="BG7" s="215" t="s">
+      <c r="BG7" s="216" t="s">
         <v>189</v>
       </c>
-      <c r="BH7" s="216" t="s">
+      <c r="BH7" s="217" t="s">
         <v>40</v>
       </c>
-      <c r="BI7" s="217" t="s">
+      <c r="BI7" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="BJ7" s="218" t="s">
+      <c r="BJ7" s="219" t="s">
         <v>40</v>
       </c>
-      <c r="BK7" s="219" t="s">
+      <c r="BK7" s="220" t="s">
         <v>41</v>
       </c>
-      <c r="BL7" s="220" t="s">
+      <c r="BL7" s="221" t="s">
         <v>40</v>
       </c>
-      <c r="BM7" s="217" t="s">
+      <c r="BM7" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="BN7" s="176"/>
+      <c r="BN7" s="177"/>
     </row>
-    <row r="8" s="103" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="103" t="s">
+    <row r="8" s="105" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="103" t="s">
+      <c r="H8" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="103" t="s">
+      <c r="K8" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="103" t="s">
+      <c r="L8" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="103" t="s">
+      <c r="M8" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="103" t="s">
+      <c r="N8" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="103" t="s">
+      <c r="O8" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="103" t="s">
+      <c r="P8" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="103" t="s">
+      <c r="Q8" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="103" t="s">
+      <c r="R8" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="103" t="s">
+      <c r="S8" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="T8" s="103" t="s">
+      <c r="T8" s="105" t="s">
         <v>191</v>
       </c>
-      <c r="U8" s="103" t="s">
+      <c r="U8" s="105" t="s">
         <v>192</v>
       </c>
-      <c r="V8" s="103" t="s">
+      <c r="V8" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="W8" s="103" t="s">
+      <c r="W8" s="105" t="s">
         <v>89</v>
       </c>
-      <c r="X8" s="103" t="s">
+      <c r="X8" s="105" t="s">
         <v>90</v>
       </c>
-      <c r="Y8" s="103" t="s">
+      <c r="Y8" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="Z8" s="103" t="s">
+      <c r="Z8" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="AA8" s="103" t="s">
+      <c r="AA8" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="AB8" s="103" t="s">
+      <c r="AB8" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="AC8" s="103" t="s">
+      <c r="AC8" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="AD8" s="103" t="s">
+      <c r="AD8" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="AE8" s="103" t="s">
+      <c r="AE8" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="AF8" s="103" t="s">
+      <c r="AF8" s="105" t="s">
         <v>193</v>
       </c>
-      <c r="AG8" s="103" t="s">
+      <c r="AG8" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="AH8" s="103" t="s">
+      <c r="AH8" s="105" t="s">
         <v>194</v>
       </c>
-      <c r="AI8" s="103" t="s">
+      <c r="AI8" s="105" t="s">
         <v>195</v>
       </c>
-      <c r="AJ8" s="103" t="s">
+      <c r="AJ8" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="AK8" s="103" t="s">
+      <c r="AK8" s="105" t="s">
         <v>196</v>
       </c>
-      <c r="AL8" s="103" t="s">
+      <c r="AL8" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="AM8" s="103" t="s">
+      <c r="AM8" s="105" t="s">
         <v>197</v>
       </c>
-      <c r="AN8" s="103" t="s">
+      <c r="AN8" s="105" t="s">
         <v>198</v>
       </c>
-      <c r="AO8" s="103" t="s">
+      <c r="AO8" s="105" t="s">
         <v>199</v>
       </c>
-      <c r="AP8" s="103" t="s">
+      <c r="AP8" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="AQ8" s="103" t="s">
+      <c r="AQ8" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="AR8" s="103" t="s">
+      <c r="AR8" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="AS8" s="103" t="s">
+      <c r="AS8" s="105" t="s">
         <v>203</v>
       </c>
-      <c r="AT8" s="103" t="s">
+      <c r="AT8" s="105" t="s">
         <v>204</v>
       </c>
-      <c r="AU8" s="103" t="s">
+      <c r="AU8" s="105" t="s">
         <v>205</v>
       </c>
-      <c r="AV8" s="103" t="s">
+      <c r="AV8" s="105" t="s">
         <v>206</v>
       </c>
-      <c r="AW8" s="103" t="s">
+      <c r="AW8" s="105" t="s">
         <v>207</v>
       </c>
-      <c r="AX8" s="103" t="s">
+      <c r="AX8" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="AY8" s="103" t="s">
+      <c r="AY8" s="105" t="s">
         <v>209</v>
       </c>
-      <c r="AZ8" s="103" t="s">
+      <c r="AZ8" s="105" t="s">
         <v>210</v>
       </c>
-      <c r="BA8" s="103" t="s">
+      <c r="BA8" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="BB8" s="103" t="s">
+      <c r="BB8" s="105" t="s">
         <v>212</v>
       </c>
-      <c r="BC8" s="103" t="s">
+      <c r="BC8" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="BD8" s="103" t="s">
+      <c r="BD8" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="BE8" s="103" t="s">
+      <c r="BE8" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="BF8" s="103" t="s">
+      <c r="BF8" s="105" t="s">
         <v>213</v>
       </c>
-      <c r="BG8" s="103" t="s">
+      <c r="BG8" s="105" t="s">
         <v>214</v>
       </c>
-      <c r="BH8" s="103" t="s">
+      <c r="BH8" s="105" t="s">
         <v>215</v>
       </c>
-      <c r="BI8" s="103" t="s">
+      <c r="BI8" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="BJ8" s="103" t="s">
+      <c r="BJ8" s="105" t="s">
         <v>217</v>
       </c>
-      <c r="BK8" s="103" t="s">
+      <c r="BK8" s="105" t="s">
         <v>218</v>
       </c>
-      <c r="BL8" s="103" t="s">
+      <c r="BL8" s="105" t="s">
         <v>219</v>
       </c>
-      <c r="BM8" s="103" t="s">
+      <c r="BM8" s="105" t="s">
         <v>220</v>
       </c>
-      <c r="BN8" s="103" t="s">
+      <c r="BN8" s="105" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="221"/>
-      <c r="B9" s="221"/>
-      <c r="C9" s="221"/>
-      <c r="D9" s="221"/>
-      <c r="E9" s="221"/>
-      <c r="F9" s="221"/>
-      <c r="G9" s="221"/>
-      <c r="H9" s="221"/>
-      <c r="I9" s="221"/>
-      <c r="J9" s="221"/>
-      <c r="K9" s="221"/>
-      <c r="L9" s="221"/>
-      <c r="M9" s="221"/>
-      <c r="N9" s="221"/>
-      <c r="O9" s="221"/>
-      <c r="P9" s="221"/>
-      <c r="Q9" s="221"/>
-      <c r="R9" s="221"/>
-      <c r="S9" s="221"/>
-      <c r="T9" s="221"/>
-      <c r="U9" s="221"/>
-      <c r="V9" s="221"/>
-      <c r="W9" s="221"/>
-      <c r="X9" s="221"/>
-      <c r="Y9" s="221"/>
-      <c r="Z9" s="221"/>
-      <c r="AA9" s="221"/>
-      <c r="AB9" s="221"/>
-      <c r="AC9" s="221"/>
-      <c r="AD9" s="221"/>
-      <c r="AE9" s="221"/>
-      <c r="AF9" s="221"/>
-      <c r="AG9" s="221"/>
-      <c r="AH9" s="221"/>
-      <c r="AI9" s="221"/>
-      <c r="AJ9" s="221"/>
-      <c r="AK9" s="221"/>
-      <c r="AL9" s="221"/>
-      <c r="AM9" s="221"/>
-      <c r="AN9" s="221"/>
-      <c r="AO9" s="221"/>
-      <c r="AP9" s="221"/>
-      <c r="AQ9" s="221"/>
-      <c r="AR9" s="221"/>
-      <c r="AS9" s="221"/>
-      <c r="AT9" s="221"/>
-      <c r="AU9" s="221"/>
-      <c r="AV9" s="221"/>
-      <c r="AW9" s="221"/>
-      <c r="AX9" s="221"/>
-      <c r="AY9" s="221"/>
-      <c r="AZ9" s="221"/>
-      <c r="BA9" s="221"/>
-      <c r="BB9" s="221"/>
-      <c r="BC9" s="221"/>
-      <c r="BD9" s="221"/>
-      <c r="BE9" s="221"/>
-      <c r="BF9" s="221"/>
-      <c r="BG9" s="221"/>
-      <c r="BH9" s="221"/>
-      <c r="BI9" s="221"/>
-      <c r="BJ9" s="221"/>
-      <c r="BK9" s="221"/>
-      <c r="BL9" s="221"/>
-      <c r="BM9" s="221"/>
-      <c r="BN9" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -6894,15 +6890,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CF9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BJ8"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="100.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="63" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="0" width="100.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="25" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="29" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="35" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="44" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="100.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="63" style="0" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="0" width="100.67"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6964,19 +6968,19 @@
       <c r="G5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="166" t="s">
+      <c r="H5" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="167" t="s">
+      <c r="I5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="167" t="s">
+      <c r="J5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="168" t="s">
+      <c r="K5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="168"/>
+      <c r="L5" s="169"/>
       <c r="M5" s="16" t="s">
         <v>10</v>
       </c>
@@ -6987,24 +6991,24 @@
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
-      <c r="U5" s="105" t="s">
+      <c r="U5" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105"/>
+      <c r="V5" s="107"/>
+      <c r="W5" s="107"/>
+      <c r="X5" s="107"/>
       <c r="Y5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="Z5" s="171" t="s">
+      <c r="Z5" s="172" t="s">
         <v>221</v>
       </c>
-      <c r="AA5" s="171"/>
-      <c r="AB5" s="171"/>
-      <c r="AC5" s="181" t="s">
+      <c r="AA5" s="172"/>
+      <c r="AB5" s="172"/>
+      <c r="AC5" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="AD5" s="181"/>
+      <c r="AD5" s="182"/>
       <c r="AE5" s="18" t="s">
         <v>18</v>
       </c>
@@ -7036,14 +7040,14 @@
       <c r="AU5" s="14"/>
       <c r="AV5" s="14"/>
       <c r="AW5" s="14"/>
-      <c r="AX5" s="174" t="s">
+      <c r="AX5" s="175" t="s">
         <v>172</v>
       </c>
-      <c r="AY5" s="174"/>
-      <c r="AZ5" s="174"/>
-      <c r="BA5" s="174"/>
-      <c r="BB5" s="174"/>
-      <c r="BC5" s="174"/>
+      <c r="AY5" s="175"/>
+      <c r="AZ5" s="175"/>
+      <c r="BA5" s="175"/>
+      <c r="BB5" s="175"/>
+      <c r="BC5" s="175"/>
       <c r="BD5" s="225" t="s">
         <v>222</v>
       </c>
@@ -7078,19 +7082,19 @@
       <c r="G6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="166" t="n">
+      <c r="H6" s="168" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="167" t="n">
+      <c r="I6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="167" t="n">
+      <c r="J6" s="30" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="229" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="189" t="n">
+      <c r="L6" s="190" t="n">
         <v>10</v>
       </c>
       <c r="M6" s="41" t="n">
@@ -7136,10 +7140,10 @@
       <c r="AC6" s="231" t="n">
         <v>33</v>
       </c>
-      <c r="AD6" s="115" t="n">
+      <c r="AD6" s="117" t="n">
         <v>34</v>
       </c>
-      <c r="AE6" s="114" t="n">
+      <c r="AE6" s="116" t="n">
         <v>41</v>
       </c>
       <c r="AF6" s="232" t="n">
@@ -7175,7 +7179,7 @@
       <c r="AP6" s="232" t="n">
         <v>114</v>
       </c>
-      <c r="AQ6" s="114" t="n">
+      <c r="AQ6" s="116" t="n">
         <v>38</v>
       </c>
       <c r="AR6" s="235" t="n">
@@ -7248,12 +7252,12 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="236"/>
-      <c r="I7" s="167"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="177" t="s">
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="178" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="189" t="s">
+      <c r="L7" s="190" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="16" t="s">
@@ -7288,10 +7292,10 @@
       <c r="Z7" s="237" t="s">
         <v>42</v>
       </c>
-      <c r="AA7" s="195" t="s">
+      <c r="AA7" s="196" t="s">
         <v>43</v>
       </c>
-      <c r="AB7" s="196" t="s">
+      <c r="AB7" s="197" t="s">
         <v>44</v>
       </c>
       <c r="AC7" s="74" t="s">
@@ -7332,7 +7336,7 @@
       <c r="AP7" s="245" t="s">
         <v>233</v>
       </c>
-      <c r="AQ7" s="206"/>
+      <c r="AQ7" s="207"/>
       <c r="AR7" s="240" t="s">
         <v>178</v>
       </c>
@@ -7389,298 +7393,190 @@
       </c>
       <c r="BJ7" s="227"/>
     </row>
-    <row r="8" s="103" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="103" t="s">
+    <row r="8" s="105" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="103" t="s">
+      <c r="H8" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="103" t="s">
+      <c r="K8" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="103" t="s">
+      <c r="L8" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="103" t="s">
+      <c r="M8" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="103" t="s">
+      <c r="N8" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="103" t="s">
+      <c r="O8" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="103" t="s">
+      <c r="P8" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="103" t="s">
+      <c r="Q8" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="103" t="s">
+      <c r="R8" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="103" t="s">
+      <c r="S8" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="T8" s="103" t="s">
+      <c r="T8" s="105" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="103" t="s">
+      <c r="U8" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="V8" s="103" t="s">
+      <c r="V8" s="105" t="s">
         <v>234</v>
       </c>
-      <c r="W8" s="103" t="s">
+      <c r="W8" s="105" t="s">
         <v>234</v>
       </c>
-      <c r="X8" s="103" t="s">
+      <c r="X8" s="105" t="s">
         <v>234</v>
       </c>
-      <c r="Y8" s="103" t="s">
+      <c r="Y8" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="103" t="s">
+      <c r="Z8" s="105" t="s">
         <v>108</v>
       </c>
-      <c r="AA8" s="103" t="s">
+      <c r="AA8" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="103" t="s">
+      <c r="AB8" s="105" t="s">
         <v>111</v>
       </c>
-      <c r="AC8" s="103" t="s">
+      <c r="AC8" s="105" t="s">
         <v>90</v>
       </c>
-      <c r="AD8" s="103" t="s">
+      <c r="AD8" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="AE8" s="103" t="s">
+      <c r="AE8" s="105" t="s">
         <v>154</v>
       </c>
-      <c r="AF8" s="103" t="s">
+      <c r="AF8" s="105" t="s">
         <v>115</v>
       </c>
-      <c r="AG8" s="103" t="s">
+      <c r="AG8" s="105" t="s">
         <v>118</v>
       </c>
-      <c r="AH8" s="103" t="s">
+      <c r="AH8" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="AI8" s="103" t="s">
+      <c r="AI8" s="105" t="s">
         <v>207</v>
       </c>
-      <c r="AJ8" s="103" t="s">
+      <c r="AJ8" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="AK8" s="103" t="s">
+      <c r="AK8" s="105" t="s">
         <v>209</v>
       </c>
-      <c r="AL8" s="103" t="s">
+      <c r="AL8" s="105" t="s">
         <v>210</v>
       </c>
-      <c r="AM8" s="103" t="s">
+      <c r="AM8" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="AN8" s="103" t="s">
+      <c r="AN8" s="105" t="s">
         <v>212</v>
       </c>
-      <c r="AO8" s="103" t="s">
+      <c r="AO8" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="AP8" s="103" t="s">
+      <c r="AP8" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="AQ8" s="103" t="s">
+      <c r="AQ8" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="AR8" s="103" t="s">
+      <c r="AR8" s="105" t="s">
         <v>213</v>
       </c>
-      <c r="AS8" s="103" t="s">
+      <c r="AS8" s="105" t="s">
         <v>214</v>
       </c>
-      <c r="AT8" s="103" t="s">
+      <c r="AT8" s="105" t="s">
         <v>215</v>
       </c>
-      <c r="AU8" s="103" t="s">
+      <c r="AU8" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="AV8" s="103" t="s">
+      <c r="AV8" s="105" t="s">
         <v>217</v>
       </c>
-      <c r="AW8" s="103" t="s">
+      <c r="AW8" s="105" t="s">
         <v>218</v>
       </c>
-      <c r="AX8" s="103" t="s">
+      <c r="AX8" s="105" t="s">
         <v>219</v>
       </c>
-      <c r="AY8" s="103" t="s">
+      <c r="AY8" s="105" t="s">
         <v>220</v>
       </c>
-      <c r="AZ8" s="103" t="s">
+      <c r="AZ8" s="105" t="s">
         <v>235</v>
       </c>
-      <c r="BA8" s="103" t="s">
+      <c r="BA8" s="105" t="s">
         <v>236</v>
       </c>
-      <c r="BB8" s="103" t="s">
+      <c r="BB8" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="BC8" s="103" t="s">
+      <c r="BC8" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="BD8" s="103" t="s">
+      <c r="BD8" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="BE8" s="103" t="s">
+      <c r="BE8" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="BF8" s="103" t="s">
+      <c r="BF8" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="BG8" s="103" t="s">
+      <c r="BG8" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="BH8" s="103" t="s">
+      <c r="BH8" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="BI8" s="103" t="s">
+      <c r="BI8" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="BJ8" s="103" t="s">
+      <c r="BJ8" s="105" t="s">
         <v>124</v>
       </c>
-      <c r="BK8" s="0"/>
-      <c r="BL8" s="0"/>
-      <c r="BM8" s="0"/>
-      <c r="BN8" s="0"/>
-      <c r="BO8" s="0"/>
-      <c r="BP8" s="0"/>
-      <c r="BQ8" s="0"/>
-      <c r="BR8" s="0"/>
-      <c r="BS8" s="0"/>
-      <c r="BT8" s="0"/>
-      <c r="BU8" s="0"/>
-      <c r="BV8" s="0"/>
-      <c r="BW8" s="0"/>
-      <c r="BX8" s="0"/>
-      <c r="BY8" s="0"/>
-      <c r="BZ8" s="0"/>
-      <c r="CA8" s="0"/>
-      <c r="CB8" s="0"/>
-      <c r="CC8" s="0"/>
-      <c r="CD8" s="0"/>
-      <c r="CE8" s="0"/>
-      <c r="CF8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="221"/>
-      <c r="B9" s="221"/>
-      <c r="C9" s="221"/>
-      <c r="D9" s="221"/>
-      <c r="E9" s="221"/>
-      <c r="F9" s="221"/>
-      <c r="G9" s="221"/>
-      <c r="H9" s="221"/>
-      <c r="I9" s="221"/>
-      <c r="J9" s="221"/>
-      <c r="K9" s="221"/>
-      <c r="L9" s="221"/>
-      <c r="M9" s="221"/>
-      <c r="N9" s="221"/>
-      <c r="O9" s="221"/>
-      <c r="P9" s="221"/>
-      <c r="Q9" s="221"/>
-      <c r="R9" s="221"/>
-      <c r="S9" s="221"/>
-      <c r="T9" s="221"/>
-      <c r="U9" s="221"/>
-      <c r="V9" s="221"/>
-      <c r="W9" s="221"/>
-      <c r="X9" s="221"/>
-      <c r="Y9" s="221"/>
-      <c r="Z9" s="221"/>
-      <c r="AA9" s="221"/>
-      <c r="AB9" s="221"/>
-      <c r="AC9" s="221"/>
-      <c r="AD9" s="221"/>
-      <c r="AE9" s="221"/>
-      <c r="AF9" s="221"/>
-      <c r="AG9" s="221"/>
-      <c r="AH9" s="221"/>
-      <c r="AI9" s="221"/>
-      <c r="AJ9" s="221"/>
-      <c r="AK9" s="221"/>
-      <c r="AL9" s="221"/>
-      <c r="AM9" s="221"/>
-      <c r="AN9" s="221"/>
-      <c r="AO9" s="221"/>
-      <c r="AP9" s="221"/>
-      <c r="AQ9" s="221"/>
-      <c r="AR9" s="221"/>
-      <c r="AS9" s="221"/>
-      <c r="AT9" s="221"/>
-      <c r="AU9" s="221"/>
-      <c r="AV9" s="221"/>
-      <c r="AW9" s="221"/>
-      <c r="AX9" s="221"/>
-      <c r="AY9" s="221"/>
-      <c r="AZ9" s="221"/>
-      <c r="BA9" s="221"/>
-      <c r="BB9" s="221"/>
-      <c r="BC9" s="221"/>
-      <c r="BD9" s="221"/>
-      <c r="BE9" s="221"/>
-      <c r="BF9" s="221"/>
-      <c r="BG9" s="221"/>
-      <c r="BH9" s="221"/>
-      <c r="BI9" s="221"/>
-      <c r="BJ9" s="221"/>
-      <c r="BK9" s="221"/>
-      <c r="BL9" s="221"/>
-      <c r="BM9" s="221"/>
-      <c r="BN9" s="221"/>
-      <c r="BO9" s="221"/>
-      <c r="BP9" s="221"/>
-      <c r="BQ9" s="221"/>
-      <c r="BR9" s="221"/>
-      <c r="BS9" s="221"/>
-      <c r="BT9" s="221"/>
-      <c r="BU9" s="221"/>
-      <c r="BV9" s="221"/>
-      <c r="BW9" s="221"/>
-      <c r="BX9" s="221"/>
-      <c r="BY9" s="221"/>
-      <c r="BZ9" s="221"/>
-      <c r="CA9" s="221"/>
-      <c r="CB9" s="221"/>
-      <c r="CC9" s="221"/>
-      <c r="CD9" s="221"/>
-      <c r="CE9" s="221"/>
-      <c r="CF9" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/excel_templates/templates.xlsx
+++ b/excel_templates/templates.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Футбол исход" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="Хоккей 24" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Футбол тотал" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Хоккей тотал" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Футбол 60" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="HTML_1" vbProcedure="false">'Футбол исход'!$A$5:$BK$7</definedName>
@@ -21,6 +22,8 @@
     <definedName function="false" hidden="false" name="HTML_tables" vbProcedure="false">#ref!</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="HTML_1" vbProcedure="false">'Футбол 24'!$A$5:$BK$7</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="HTML_all" vbProcedure="false">'Футбол 24'!$A$5:$BM$7</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="HTML_1" vbProcedure="false">'Футбол 60'!$A$5:$AG$7</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="HTML_all" vbProcedure="false">'Футбол 60'!$A$5:$AH$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -487,8 +490,84 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">beforerow{% for row in rows %}</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>16</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>24</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>4</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">beforerow{% endfor %}</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>16</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>32</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>24</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="245">
   <si>
     <t xml:space="preserve">FHB STAT</t>
   </si>
@@ -1254,6 +1333,15 @@
   </si>
   <si>
     <t xml:space="preserve">{{ row.get('132') }}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФУТБОЛ 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФУТБОЛ 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИСХОД МАТЧА</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1504,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999"/>
+        <fgColor theme="6" tint="0.5998"/>
         <bgColor rgb="FFD1DFB3"/>
       </patternFill>
     </fill>
@@ -1434,7 +1522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999"/>
+        <fgColor theme="3" tint="0.7998"/>
         <bgColor rgb="FFC8E1FC"/>
       </patternFill>
     </fill>
@@ -1458,7 +1546,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999"/>
+        <fgColor theme="7" tint="0.7998"/>
         <bgColor rgb="FFE2E3F6"/>
       </patternFill>
     </fill>
@@ -1506,7 +1594,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.3999"/>
+        <fgColor theme="6" tint="0.3998"/>
         <bgColor rgb="FFD1DFB3"/>
       </patternFill>
     </fill>
@@ -1542,7 +1630,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999"/>
+        <fgColor theme="7" tint="0.5998"/>
         <bgColor rgb="FFD8D4BA"/>
       </patternFill>
     </fill>
@@ -1554,7 +1642,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999"/>
+        <fgColor theme="9" tint="0.5998"/>
         <bgColor rgb="FFF7D0AF"/>
       </patternFill>
     </fill>
@@ -1686,436 +1774,440 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="24" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="25" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="26" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="28" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="28" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="31" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="31" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="27" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="27" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="28" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="28" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="32" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="33" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="33" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="31" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="31" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="34" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="34" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="29" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="30" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="34" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="34" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="32" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2375,737 +2467,737 @@
   <dimension ref="A1:BL9"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="46" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="150.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="46" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="150.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="2" width="11.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="7" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="15" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="16" t="s">
+      <c r="T5" s="16"/>
+      <c r="U5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="16"/>
-      <c r="W5" s="17" t="s">
+      <c r="V5" s="17"/>
+      <c r="W5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="18" t="s">
+      <c r="X5" s="18"/>
+      <c r="Y5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Z5" s="19" t="s">
+      <c r="Z5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
-      <c r="AC5" s="20" t="s">
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="16" t="s">
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="21" t="s">
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AI5" s="22" t="s">
+      <c r="AI5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="23" t="s">
+      <c r="AJ5" s="23"/>
+      <c r="AK5" s="23"/>
+      <c r="AL5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="16" t="s">
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AO5" s="24" t="s">
+      <c r="AO5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AP5" s="24"/>
-      <c r="AQ5" s="16" t="s">
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AS5" s="25"/>
-      <c r="AT5" s="26" t="s">
+      <c r="AS5" s="26"/>
+      <c r="AT5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AU5" s="27" t="s">
+      <c r="AU5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="16" t="s">
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="AY5" s="28" t="s">
+      <c r="AY5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="16" t="s">
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="BC5" s="29" t="s">
+      <c r="BC5" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="30" t="s">
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="32" t="n">
+    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="33" t="n">
+      <c r="J6" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="36" t="n">
+      <c r="O6" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="36" t="n">
+      <c r="Q6" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="37" t="n">
+      <c r="R6" s="38" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="38" t="n">
+      <c r="S6" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="T6" s="38" t="n">
+      <c r="T6" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="U6" s="39" t="n">
+      <c r="U6" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="V6" s="39" t="n">
+      <c r="V6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="W6" s="40" t="n">
+      <c r="W6" s="41" t="n">
         <v>22</v>
       </c>
-      <c r="X6" s="40" t="n">
+      <c r="X6" s="41" t="n">
         <v>23</v>
       </c>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="41" t="n">
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="AA6" s="41" t="n">
+      <c r="AA6" s="42" t="n">
         <v>26</v>
       </c>
-      <c r="AB6" s="41" t="n">
+      <c r="AB6" s="42" t="n">
         <v>27</v>
       </c>
-      <c r="AC6" s="42" t="n">
+      <c r="AC6" s="43" t="n">
         <v>32</v>
       </c>
-      <c r="AD6" s="42" t="n">
+      <c r="AD6" s="43" t="n">
         <v>33</v>
       </c>
-      <c r="AE6" s="42" t="n">
+      <c r="AE6" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="AF6" s="39" t="n">
+      <c r="AF6" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="AG6" s="39" t="n">
+      <c r="AG6" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="AH6" s="43" t="n">
+      <c r="AH6" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="AI6" s="44" t="n">
+      <c r="AI6" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="AJ6" s="44" t="n">
+      <c r="AJ6" s="45" t="n">
         <v>36</v>
       </c>
-      <c r="AK6" s="44" t="n">
+      <c r="AK6" s="45" t="n">
         <v>37</v>
       </c>
-      <c r="AL6" s="45" t="n">
+      <c r="AL6" s="46" t="n">
         <v>38</v>
       </c>
-      <c r="AM6" s="45" t="n">
+      <c r="AM6" s="46" t="n">
         <v>39</v>
       </c>
-      <c r="AN6" s="46" t="n">
+      <c r="AN6" s="47" t="n">
         <v>127</v>
       </c>
-      <c r="AO6" s="47" t="n">
+      <c r="AO6" s="48" t="n">
         <v>113</v>
       </c>
-      <c r="AP6" s="47" t="n">
+      <c r="AP6" s="48" t="n">
         <v>114</v>
       </c>
-      <c r="AQ6" s="46" t="n">
+      <c r="AQ6" s="47" t="n">
         <v>128</v>
       </c>
-      <c r="AR6" s="48" t="n">
+      <c r="AR6" s="49" t="n">
         <v>92</v>
       </c>
-      <c r="AS6" s="49" t="n">
+      <c r="AS6" s="50" t="n">
         <v>95</v>
       </c>
-      <c r="AT6" s="50" t="n">
+      <c r="AT6" s="51" t="n">
         <v>129</v>
       </c>
-      <c r="AU6" s="51" t="n">
+      <c r="AU6" s="52" t="n">
         <v>44</v>
       </c>
-      <c r="AV6" s="51" t="n">
+      <c r="AV6" s="52" t="n">
         <v>45</v>
       </c>
-      <c r="AW6" s="51" t="n">
+      <c r="AW6" s="52" t="n">
         <v>46</v>
       </c>
-      <c r="AX6" s="16" t="n">
+      <c r="AX6" s="17" t="n">
         <v>130</v>
       </c>
-      <c r="AY6" s="52" t="n">
+      <c r="AY6" s="53" t="n">
         <v>47</v>
       </c>
-      <c r="AZ6" s="52" t="n">
+      <c r="AZ6" s="53" t="n">
         <v>48</v>
       </c>
-      <c r="BA6" s="52" t="n">
+      <c r="BA6" s="53" t="n">
         <v>49</v>
       </c>
-      <c r="BB6" s="16" t="n">
+      <c r="BB6" s="17" t="n">
         <v>131</v>
       </c>
-      <c r="BC6" s="53" t="n">
+      <c r="BC6" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="BD6" s="53" t="n">
+      <c r="BD6" s="54" t="n">
         <v>51</v>
       </c>
-      <c r="BE6" s="53" t="n">
+      <c r="BE6" s="54" t="n">
         <v>52</v>
       </c>
-      <c r="BF6" s="53" t="n">
+      <c r="BF6" s="54" t="n">
         <v>53</v>
       </c>
-      <c r="BG6" s="53" t="n">
+      <c r="BG6" s="54" t="n">
         <v>54</v>
       </c>
-      <c r="BH6" s="53" t="n">
+      <c r="BH6" s="54" t="n">
         <v>55</v>
       </c>
-      <c r="BI6" s="53" t="n">
+      <c r="BI6" s="54" t="n">
         <v>56</v>
       </c>
-      <c r="BJ6" s="53" t="n">
+      <c r="BJ6" s="54" t="n">
         <v>57</v>
       </c>
-      <c r="BK6" s="53" t="n">
+      <c r="BK6" s="54" t="n">
         <v>58</v>
       </c>
-      <c r="BL6" s="30"/>
+      <c r="BL6" s="31"/>
     </row>
-    <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="55" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="56" t="s">
+      <c r="P7" s="56"/>
+      <c r="Q7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="56"/>
-      <c r="S7" s="57" t="s">
+      <c r="R7" s="57"/>
+      <c r="S7" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="57" t="s">
+      <c r="T7" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="58" t="s">
+      <c r="U7" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="V7" s="58" t="s">
+      <c r="V7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="W7" s="59" t="s">
+      <c r="W7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="X7" s="59" t="s">
+      <c r="X7" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="60" t="s">
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="AA7" s="60" t="s">
+      <c r="AA7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AB7" s="60" t="s">
+      <c r="AB7" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AC7" s="61" t="s">
+      <c r="AC7" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="AD7" s="61" t="s">
+      <c r="AD7" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="AE7" s="61" t="s">
+      <c r="AE7" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="AF7" s="58" t="s">
+      <c r="AF7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AG7" s="58" t="s">
+      <c r="AG7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AH7" s="21"/>
-      <c r="AI7" s="62" t="s">
+      <c r="AH7" s="22"/>
+      <c r="AI7" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AJ7" s="44" t="n">
+      <c r="AJ7" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="AK7" s="62" t="s">
+      <c r="AK7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="AL7" s="63" t="s">
+      <c r="AL7" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="AM7" s="63" t="s">
+      <c r="AM7" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="AN7" s="16"/>
-      <c r="AO7" s="47" t="s">
+      <c r="AN7" s="17"/>
+      <c r="AO7" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="AP7" s="47" t="s">
+      <c r="AP7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="AQ7" s="16"/>
-      <c r="AR7" s="48" t="s">
+      <c r="AQ7" s="17"/>
+      <c r="AR7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="AS7" s="49" t="s">
+      <c r="AS7" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="AT7" s="26"/>
-      <c r="AU7" s="64" t="s">
+      <c r="AT7" s="27"/>
+      <c r="AU7" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="AV7" s="64" t="s">
+      <c r="AV7" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="AW7" s="64" t="s">
+      <c r="AW7" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="65" t="s">
+      <c r="AX7" s="17"/>
+      <c r="AY7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="AZ7" s="65" t="s">
+      <c r="AZ7" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="BA7" s="65" t="s">
+      <c r="BA7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="BB7" s="16"/>
-      <c r="BC7" s="53" t="s">
+      <c r="BB7" s="17"/>
+      <c r="BC7" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="BD7" s="53" t="s">
+      <c r="BD7" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="BE7" s="53" t="s">
+      <c r="BE7" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="BF7" s="53" t="s">
+      <c r="BF7" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="BG7" s="53" t="s">
+      <c r="BG7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="BH7" s="53" t="s">
+      <c r="BH7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="BI7" s="53" t="s">
+      <c r="BI7" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="BJ7" s="53" t="s">
+      <c r="BJ7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="BK7" s="53" t="s">
+      <c r="BK7" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="BL7" s="30"/>
+      <c r="BL7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="66" t="s">
+      <c r="H8" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="66" t="s">
+      <c r="I8" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="66" t="s">
+      <c r="J8" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="66" t="s">
+      <c r="K8" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="66" t="s">
+      <c r="L8" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="66" t="s">
+      <c r="M8" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="66" t="s">
+      <c r="N8" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="66" t="s">
+      <c r="O8" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="66" t="s">
+      <c r="Q8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="66" t="s">
+      <c r="R8" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="66" t="s">
+      <c r="S8" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T8" s="66" t="s">
+      <c r="T8" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="U8" s="66" t="s">
+      <c r="U8" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="V8" s="66" t="s">
+      <c r="V8" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="66" t="s">
+      <c r="W8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="66" t="s">
+      <c r="X8" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="Z8" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AA8" s="66" t="s">
+      <c r="AA8" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AB8" s="66" t="s">
+      <c r="AB8" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="AC8" s="66" t="s">
+      <c r="AC8" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="AD8" s="66" t="s">
+      <c r="AD8" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="AE8" s="66" t="s">
+      <c r="AE8" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="AF8" s="66" t="s">
+      <c r="AF8" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="66" t="s">
+      <c r="AG8" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="AH8" s="66" t="s">
+      <c r="AH8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="66" t="s">
+      <c r="AI8" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="AJ8" s="66" t="s">
+      <c r="AJ8" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="AK8" s="66" t="s">
+      <c r="AK8" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AL8" s="66" t="s">
+      <c r="AL8" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="AM8" s="66" t="s">
+      <c r="AM8" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="AN8" s="66" t="s">
+      <c r="AN8" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="AO8" s="66" t="s">
+      <c r="AO8" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="AP8" s="66" t="s">
+      <c r="AP8" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="AQ8" s="66" t="s">
+      <c r="AQ8" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="AR8" s="66" t="s">
+      <c r="AR8" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="AS8" s="66" t="s">
+      <c r="AS8" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="AT8" s="66" t="s">
+      <c r="AT8" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="66" t="s">
+      <c r="AU8" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="AV8" s="66" t="s">
+      <c r="AV8" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="AW8" s="66" t="s">
+      <c r="AW8" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="AX8" s="66" t="s">
+      <c r="AX8" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="AY8" s="66" t="s">
+      <c r="AY8" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="AZ8" s="66" t="s">
+      <c r="AZ8" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="BA8" s="66" t="s">
+      <c r="BA8" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="BB8" s="66" t="s">
+      <c r="BB8" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="BC8" s="66" t="s">
+      <c r="BC8" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="BD8" s="66" t="s">
+      <c r="BD8" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="BE8" s="66" t="s">
+      <c r="BE8" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="BF8" s="66" t="s">
+      <c r="BF8" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="BG8" s="66" t="s">
+      <c r="BG8" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="BH8" s="66" t="s">
+      <c r="BH8" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="BI8" s="66" t="s">
+      <c r="BI8" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="BJ8" s="66" t="s">
+      <c r="BJ8" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="BK8" s="66" t="s">
+      <c r="BK8" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="BL8" s="66" t="s">
+      <c r="BL8" s="67" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B2:H3"/>
@@ -3152,804 +3244,804 @@
   <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="46" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="150.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="32" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="35" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="44" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="46" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="150.71"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="7" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="15" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="16" t="s">
+      <c r="T5" s="16"/>
+      <c r="U5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="16"/>
-      <c r="W5" s="17" t="s">
+      <c r="V5" s="17"/>
+      <c r="W5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="18" t="s">
+      <c r="X5" s="18"/>
+      <c r="Y5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Z5" s="19" t="s">
+      <c r="Z5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
-      <c r="AC5" s="20" t="s">
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="16" t="s">
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="21" t="s">
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AI5" s="22" t="s">
+      <c r="AI5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="23" t="s">
+      <c r="AJ5" s="23"/>
+      <c r="AK5" s="23"/>
+      <c r="AL5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="16" t="s">
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AO5" s="24" t="s">
+      <c r="AO5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AP5" s="24"/>
-      <c r="AQ5" s="16" t="s">
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AS5" s="25"/>
-      <c r="AT5" s="26" t="s">
+      <c r="AS5" s="26"/>
+      <c r="AT5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AU5" s="27" t="s">
+      <c r="AU5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="16" t="s">
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="AY5" s="28" t="s">
+      <c r="AY5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="16" t="s">
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="BC5" s="29" t="s">
+      <c r="BC5" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="30" t="s">
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="32" t="n">
+    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="33" t="n">
+      <c r="J6" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="36" t="n">
+      <c r="O6" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="36" t="n">
+      <c r="Q6" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="37" t="n">
+      <c r="R6" s="38" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="38" t="n">
+      <c r="S6" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="T6" s="38" t="n">
+      <c r="T6" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="U6" s="39" t="n">
+      <c r="U6" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="V6" s="39" t="n">
+      <c r="V6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="W6" s="40" t="n">
+      <c r="W6" s="41" t="n">
         <v>22</v>
       </c>
-      <c r="X6" s="40" t="n">
+      <c r="X6" s="41" t="n">
         <v>23</v>
       </c>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="41" t="n">
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="AA6" s="41" t="n">
+      <c r="AA6" s="42" t="n">
         <v>26</v>
       </c>
-      <c r="AB6" s="41" t="n">
+      <c r="AB6" s="42" t="n">
         <v>27</v>
       </c>
-      <c r="AC6" s="42" t="n">
+      <c r="AC6" s="43" t="n">
         <v>32</v>
       </c>
-      <c r="AD6" s="42" t="n">
+      <c r="AD6" s="43" t="n">
         <v>33</v>
       </c>
-      <c r="AE6" s="42" t="n">
+      <c r="AE6" s="43" t="n">
         <v>34</v>
       </c>
-      <c r="AF6" s="39" t="n">
+      <c r="AF6" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="AG6" s="39" t="n">
+      <c r="AG6" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="AH6" s="43" t="n">
+      <c r="AH6" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="AI6" s="44" t="n">
+      <c r="AI6" s="45" t="n">
         <v>35</v>
       </c>
-      <c r="AJ6" s="44" t="n">
+      <c r="AJ6" s="45" t="n">
         <v>36</v>
       </c>
-      <c r="AK6" s="44" t="n">
+      <c r="AK6" s="45" t="n">
         <v>37</v>
       </c>
-      <c r="AL6" s="45" t="n">
+      <c r="AL6" s="46" t="n">
         <v>38</v>
       </c>
-      <c r="AM6" s="45" t="n">
+      <c r="AM6" s="46" t="n">
         <v>39</v>
       </c>
-      <c r="AN6" s="46" t="n">
+      <c r="AN6" s="47" t="n">
         <v>127</v>
       </c>
-      <c r="AO6" s="47" t="n">
+      <c r="AO6" s="48" t="n">
         <v>40</v>
       </c>
-      <c r="AP6" s="47" t="n">
+      <c r="AP6" s="48" t="n">
         <v>41</v>
       </c>
-      <c r="AQ6" s="46" t="n">
+      <c r="AQ6" s="47" t="n">
         <v>128</v>
       </c>
-      <c r="AR6" s="48" t="n">
+      <c r="AR6" s="49" t="n">
         <v>42</v>
       </c>
-      <c r="AS6" s="49" t="n">
+      <c r="AS6" s="50" t="n">
         <v>43</v>
       </c>
-      <c r="AT6" s="50" t="n">
+      <c r="AT6" s="51" t="n">
         <v>129</v>
       </c>
-      <c r="AU6" s="51" t="n">
+      <c r="AU6" s="52" t="n">
         <v>44</v>
       </c>
-      <c r="AV6" s="51" t="n">
+      <c r="AV6" s="52" t="n">
         <v>45</v>
       </c>
-      <c r="AW6" s="51" t="n">
+      <c r="AW6" s="52" t="n">
         <v>46</v>
       </c>
-      <c r="AX6" s="16" t="n">
+      <c r="AX6" s="17" t="n">
         <v>130</v>
       </c>
-      <c r="AY6" s="52" t="n">
+      <c r="AY6" s="53" t="n">
         <v>47</v>
       </c>
-      <c r="AZ6" s="52" t="n">
+      <c r="AZ6" s="53" t="n">
         <v>48</v>
       </c>
-      <c r="BA6" s="52" t="n">
+      <c r="BA6" s="53" t="n">
         <v>49</v>
       </c>
-      <c r="BB6" s="16" t="n">
+      <c r="BB6" s="17" t="n">
         <v>131</v>
       </c>
-      <c r="BC6" s="53" t="n">
+      <c r="BC6" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="BD6" s="53" t="n">
+      <c r="BD6" s="54" t="n">
         <v>51</v>
       </c>
-      <c r="BE6" s="53" t="n">
+      <c r="BE6" s="54" t="n">
         <v>52</v>
       </c>
-      <c r="BF6" s="53" t="n">
+      <c r="BF6" s="54" t="n">
         <v>53</v>
       </c>
-      <c r="BG6" s="53" t="n">
+      <c r="BG6" s="54" t="n">
         <v>54</v>
       </c>
-      <c r="BH6" s="53" t="n">
+      <c r="BH6" s="54" t="n">
         <v>55</v>
       </c>
-      <c r="BI6" s="53" t="n">
+      <c r="BI6" s="54" t="n">
         <v>56</v>
       </c>
-      <c r="BJ6" s="53" t="n">
+      <c r="BJ6" s="54" t="n">
         <v>57</v>
       </c>
-      <c r="BK6" s="53" t="n">
+      <c r="BK6" s="54" t="n">
         <v>58</v>
       </c>
-      <c r="BL6" s="30"/>
+      <c r="BL6" s="31"/>
     </row>
-    <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="55" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="56" t="s">
+      <c r="P7" s="56"/>
+      <c r="Q7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="56"/>
-      <c r="S7" s="57" t="s">
+      <c r="R7" s="57"/>
+      <c r="S7" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="57" t="s">
+      <c r="T7" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="U7" s="58" t="s">
+      <c r="U7" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="V7" s="58" t="s">
+      <c r="V7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="W7" s="59" t="s">
+      <c r="W7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="X7" s="59" t="s">
+      <c r="X7" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="60" t="s">
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="AA7" s="60" t="s">
+      <c r="AA7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AB7" s="60" t="s">
+      <c r="AB7" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AC7" s="61" t="s">
+      <c r="AC7" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="AD7" s="61" t="s">
+      <c r="AD7" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="AE7" s="61" t="s">
+      <c r="AE7" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="AF7" s="58" t="s">
+      <c r="AF7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AG7" s="58" t="s">
+      <c r="AG7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AH7" s="21"/>
-      <c r="AI7" s="62" t="s">
+      <c r="AH7" s="22"/>
+      <c r="AI7" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AJ7" s="44" t="n">
+      <c r="AJ7" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="AK7" s="62" t="s">
+      <c r="AK7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="AL7" s="63" t="s">
+      <c r="AL7" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="AM7" s="63" t="s">
+      <c r="AM7" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="AN7" s="16"/>
-      <c r="AO7" s="47" t="s">
+      <c r="AN7" s="17"/>
+      <c r="AO7" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="AP7" s="47" t="s">
+      <c r="AP7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="AQ7" s="16"/>
-      <c r="AR7" s="48" t="s">
+      <c r="AQ7" s="17"/>
+      <c r="AR7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="AS7" s="49" t="s">
+      <c r="AS7" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="AT7" s="26"/>
-      <c r="AU7" s="64" t="s">
+      <c r="AT7" s="27"/>
+      <c r="AU7" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="AV7" s="64" t="s">
+      <c r="AV7" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="AW7" s="64" t="s">
+      <c r="AW7" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="65" t="s">
+      <c r="AX7" s="17"/>
+      <c r="AY7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="AZ7" s="65" t="s">
+      <c r="AZ7" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="BA7" s="65" t="s">
+      <c r="BA7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="BB7" s="16"/>
-      <c r="BC7" s="53" t="s">
+      <c r="BB7" s="17"/>
+      <c r="BC7" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="BD7" s="53" t="s">
+      <c r="BD7" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="BE7" s="53" t="s">
+      <c r="BE7" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="BF7" s="53" t="s">
+      <c r="BF7" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="BG7" s="53" t="s">
+      <c r="BG7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="BH7" s="53" t="s">
+      <c r="BH7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="BI7" s="53" t="s">
+      <c r="BI7" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="BJ7" s="53" t="s">
+      <c r="BJ7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="BK7" s="53" t="s">
+      <c r="BK7" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="BL7" s="30"/>
+      <c r="BL7" s="31"/>
     </row>
-    <row r="8" s="67" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+    <row r="8" s="68" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="66" t="s">
+      <c r="H8" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="66" t="s">
+      <c r="I8" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="66" t="s">
+      <c r="J8" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="66" t="s">
+      <c r="K8" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="66" t="s">
+      <c r="L8" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="66" t="s">
+      <c r="M8" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="66" t="s">
+      <c r="N8" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="66" t="s">
+      <c r="O8" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="66" t="s">
+      <c r="Q8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="66" t="s">
+      <c r="R8" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="66" t="s">
+      <c r="S8" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T8" s="66" t="s">
+      <c r="T8" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="U8" s="66" t="s">
+      <c r="U8" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="V8" s="66" t="s">
+      <c r="V8" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="66" t="s">
+      <c r="W8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="X8" s="66" t="s">
+      <c r="X8" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="Z8" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AA8" s="66" t="s">
+      <c r="AA8" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AB8" s="66" t="s">
+      <c r="AB8" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="AC8" s="66" t="s">
+      <c r="AC8" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="AD8" s="66" t="s">
+      <c r="AD8" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="AE8" s="66" t="s">
+      <c r="AE8" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="AF8" s="66" t="s">
+      <c r="AF8" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="66" t="s">
+      <c r="AG8" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="AH8" s="66" t="s">
+      <c r="AH8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="66" t="s">
+      <c r="AI8" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="AJ8" s="66" t="s">
+      <c r="AJ8" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="AK8" s="66" t="s">
+      <c r="AK8" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AL8" s="66" t="s">
+      <c r="AL8" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="AM8" s="66" t="s">
+      <c r="AM8" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="AN8" s="66" t="s">
+      <c r="AN8" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="AO8" s="66" t="s">
+      <c r="AO8" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="AP8" s="66" t="s">
+      <c r="AP8" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="AQ8" s="66" t="s">
+      <c r="AQ8" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="AR8" s="66" t="s">
+      <c r="AR8" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="AS8" s="66" t="s">
+      <c r="AS8" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="AT8" s="66" t="s">
+      <c r="AT8" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="66" t="s">
+      <c r="AU8" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="AV8" s="66" t="s">
+      <c r="AV8" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="AW8" s="66" t="s">
+      <c r="AW8" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="AX8" s="66" t="s">
+      <c r="AX8" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="AY8" s="66" t="s">
+      <c r="AY8" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="AZ8" s="66" t="s">
+      <c r="AZ8" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="BA8" s="66" t="s">
+      <c r="BA8" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="BB8" s="66" t="s">
+      <c r="BB8" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="BC8" s="66" t="s">
+      <c r="BC8" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="BD8" s="66" t="s">
+      <c r="BD8" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="BE8" s="66" t="s">
+      <c r="BE8" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="BF8" s="66" t="s">
+      <c r="BF8" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="BG8" s="66" t="s">
+      <c r="BG8" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="BH8" s="66" t="s">
+      <c r="BH8" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="BI8" s="66" t="s">
+      <c r="BI8" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="BJ8" s="66" t="s">
+      <c r="BJ8" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="BK8" s="66" t="s">
+      <c r="BK8" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="BL8" s="66" t="s">
+      <c r="BL8" s="67" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="1"/>
-      <c r="AR9" s="1"/>
-      <c r="AS9" s="1"/>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
-      <c r="AW9" s="1"/>
-      <c r="AX9" s="1"/>
-      <c r="AY9" s="1"/>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
-      <c r="BC9" s="1"/>
-      <c r="BD9" s="1"/>
-      <c r="BE9" s="1"/>
-      <c r="BF9" s="1"/>
-      <c r="BG9" s="1"/>
-      <c r="BH9" s="1"/>
-      <c r="BI9" s="1"/>
-      <c r="BJ9" s="1"/>
-      <c r="BK9" s="1"/>
-      <c r="BL9" s="1"/>
-      <c r="BM9" s="1"/>
-      <c r="BN9" s="1"/>
-      <c r="BO9" s="1"/>
-      <c r="BP9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
+      <c r="AU9" s="2"/>
+      <c r="AV9" s="2"/>
+      <c r="AW9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="AY9" s="2"/>
+      <c r="AZ9" s="2"/>
+      <c r="BA9" s="2"/>
+      <c r="BB9" s="2"/>
+      <c r="BC9" s="2"/>
+      <c r="BD9" s="2"/>
+      <c r="BE9" s="2"/>
+      <c r="BF9" s="2"/>
+      <c r="BG9" s="2"/>
+      <c r="BH9" s="2"/>
+      <c r="BI9" s="2"/>
+      <c r="BJ9" s="2"/>
+      <c r="BK9" s="2"/>
+      <c r="BL9" s="2"/>
+      <c r="BM9" s="2"/>
+      <c r="BN9" s="2"/>
+      <c r="BO9" s="2"/>
+      <c r="BP9" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3997,776 +4089,776 @@
   <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="50" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="53" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="150.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="50" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="53" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="150.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="69" style="2" width="11.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="7" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="54" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="15" t="s">
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="68" t="s">
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-      <c r="AA5" s="16" t="s">
+      <c r="Y5" s="69"/>
+      <c r="Z5" s="69"/>
+      <c r="AA5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="69" t="s">
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="AD5" s="69"/>
-      <c r="AE5" s="17" t="s">
+      <c r="AD5" s="70"/>
+      <c r="AE5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="18" t="s">
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="AH5" s="19" t="s">
+      <c r="AH5" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="19"/>
-      <c r="AK5" s="20" t="s">
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="16" t="s">
+      <c r="AL5" s="21"/>
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="21" t="s">
+      <c r="AO5" s="17"/>
+      <c r="AP5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AQ5" s="22" t="s">
+      <c r="AQ5" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AR5" s="22"/>
-      <c r="AS5" s="70" t="s">
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="23" t="s">
+      <c r="AT5" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="70" t="s">
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="AX5" s="24" t="s">
+      <c r="AX5" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="AY5" s="24"/>
-      <c r="AZ5" s="24"/>
-      <c r="BA5" s="27" t="s">
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="70" t="s">
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="BE5" s="28" t="s">
+      <c r="BE5" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="70" t="s">
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="BI5" s="71" t="s">
+      <c r="BI5" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="BJ5" s="71"/>
-      <c r="BK5" s="71"/>
-      <c r="BL5" s="70" t="s">
+      <c r="BJ5" s="72"/>
+      <c r="BK5" s="72"/>
+      <c r="BL5" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="BM5" s="25" t="s">
+      <c r="BM5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="BN5" s="25"/>
-      <c r="BO5" s="70" t="s">
+      <c r="BN5" s="26"/>
+      <c r="BO5" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="BP5" s="30" t="s">
+      <c r="BP5" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="32" t="n">
+    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="33" t="n">
+      <c r="J6" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="35" t="n">
+      <c r="Q6" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="35" t="n">
+      <c r="R6" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="35" t="n">
+      <c r="S6" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="T6" s="35" t="n">
+      <c r="T6" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="38" t="n">
+      <c r="U6" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="38" t="n">
+      <c r="V6" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="W6" s="38" t="n">
+      <c r="W6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="X6" s="72" t="n">
+      <c r="X6" s="73" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="72" t="n">
+      <c r="Y6" s="73" t="n">
         <v>43</v>
       </c>
-      <c r="Z6" s="72" t="n">
+      <c r="Z6" s="73" t="n">
         <v>29</v>
       </c>
-      <c r="AA6" s="39" t="n">
+      <c r="AA6" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="AB6" s="39" t="n">
+      <c r="AB6" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="AC6" s="73" t="n">
+      <c r="AC6" s="74" t="n">
         <v>25</v>
       </c>
-      <c r="AD6" s="73" t="n">
+      <c r="AD6" s="74" t="n">
         <v>26</v>
       </c>
-      <c r="AE6" s="40" t="n">
+      <c r="AE6" s="41" t="n">
         <v>27</v>
       </c>
-      <c r="AF6" s="40" t="n">
+      <c r="AF6" s="41" t="n">
         <v>28</v>
       </c>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="41" t="n">
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="AI6" s="41" t="n">
+      <c r="AI6" s="42" t="n">
         <v>31</v>
       </c>
-      <c r="AJ6" s="41" t="n">
+      <c r="AJ6" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="AK6" s="42" t="n">
+      <c r="AK6" s="43" t="n">
         <v>45</v>
       </c>
-      <c r="AL6" s="42" t="n">
+      <c r="AL6" s="43" t="n">
         <v>46</v>
       </c>
-      <c r="AM6" s="42" t="n">
+      <c r="AM6" s="43" t="n">
         <v>47</v>
       </c>
-      <c r="AN6" s="39" t="n">
+      <c r="AN6" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="AO6" s="39" t="n">
+      <c r="AO6" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="AP6" s="43" t="n">
+      <c r="AP6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="AQ6" s="44" t="n">
+      <c r="AQ6" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="AR6" s="44" t="n">
+      <c r="AR6" s="45" t="n">
         <v>49</v>
       </c>
-      <c r="AS6" s="74" t="n">
+      <c r="AS6" s="75" t="n">
         <v>36</v>
       </c>
-      <c r="AT6" s="45" t="n">
+      <c r="AT6" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="AU6" s="45" t="n">
+      <c r="AU6" s="46" t="n">
         <v>51</v>
       </c>
-      <c r="AV6" s="45" t="n">
+      <c r="AV6" s="46" t="n">
         <v>52</v>
       </c>
-      <c r="AW6" s="74" t="n">
+      <c r="AW6" s="75" t="n">
         <v>37</v>
       </c>
-      <c r="AX6" s="75" t="n">
+      <c r="AX6" s="76" t="n">
         <v>53</v>
       </c>
-      <c r="AY6" s="75" t="n">
+      <c r="AY6" s="76" t="n">
         <v>54</v>
       </c>
-      <c r="AZ6" s="75" t="n">
+      <c r="AZ6" s="76" t="n">
         <v>55</v>
       </c>
-      <c r="BA6" s="51" t="n">
+      <c r="BA6" s="52" t="n">
         <v>56</v>
       </c>
-      <c r="BB6" s="51" t="n">
+      <c r="BB6" s="52" t="n">
         <v>57</v>
       </c>
-      <c r="BC6" s="51" t="n">
+      <c r="BC6" s="52" t="n">
         <v>58</v>
       </c>
-      <c r="BD6" s="74" t="n">
+      <c r="BD6" s="75" t="n">
         <v>137</v>
       </c>
-      <c r="BE6" s="52" t="n">
+      <c r="BE6" s="53" t="n">
         <v>59</v>
       </c>
-      <c r="BF6" s="52" t="n">
+      <c r="BF6" s="53" t="n">
         <v>60</v>
       </c>
-      <c r="BG6" s="52" t="n">
+      <c r="BG6" s="53" t="n">
         <v>61</v>
       </c>
-      <c r="BH6" s="74" t="n">
+      <c r="BH6" s="75" t="n">
         <v>138</v>
       </c>
-      <c r="BI6" s="76" t="n">
+      <c r="BI6" s="77" t="n">
         <v>62</v>
       </c>
-      <c r="BJ6" s="76" t="n">
+      <c r="BJ6" s="77" t="n">
         <v>63</v>
       </c>
-      <c r="BK6" s="76" t="n">
+      <c r="BK6" s="77" t="n">
         <v>64</v>
       </c>
-      <c r="BL6" s="74" t="n">
+      <c r="BL6" s="75" t="n">
         <v>139</v>
       </c>
-      <c r="BM6" s="48" t="n">
+      <c r="BM6" s="49" t="n">
         <v>65</v>
       </c>
-      <c r="BN6" s="49" t="n">
+      <c r="BN6" s="50" t="n">
         <v>66</v>
       </c>
-      <c r="BO6" s="74" t="n">
+      <c r="BO6" s="75" t="n">
         <v>38</v>
       </c>
-      <c r="BP6" s="30"/>
+      <c r="BP6" s="31"/>
     </row>
-    <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="77" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77" t="s">
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77" t="s">
+      <c r="R7" s="78"/>
+      <c r="S7" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="T7" s="77"/>
-      <c r="U7" s="57" t="s">
+      <c r="T7" s="78"/>
+      <c r="U7" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="V7" s="57"/>
-      <c r="W7" s="57" t="s">
+      <c r="V7" s="58"/>
+      <c r="W7" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="X7" s="78" t="s">
+      <c r="X7" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="Y7" s="78" t="s">
+      <c r="Y7" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="Z7" s="78" t="s">
+      <c r="Z7" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="AA7" s="58" t="s">
+      <c r="AA7" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="58" t="s">
+      <c r="AB7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="AC7" s="79" t="s">
+      <c r="AC7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="79" t="s">
+      <c r="AD7" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="59" t="s">
+      <c r="AE7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="59" t="s">
+      <c r="AF7" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="60" t="s">
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="AI7" s="60" t="s">
+      <c r="AI7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AJ7" s="60" t="s">
+      <c r="AJ7" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AK7" s="61" t="s">
+      <c r="AK7" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="AL7" s="61" t="s">
+      <c r="AL7" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="AM7" s="61" t="s">
+      <c r="AM7" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="AN7" s="58" t="s">
+      <c r="AN7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="58" t="s">
+      <c r="AO7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AP7" s="80"/>
-      <c r="AQ7" s="62" t="s">
+      <c r="AP7" s="81"/>
+      <c r="AQ7" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AR7" s="62" t="s">
+      <c r="AR7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="AS7" s="81"/>
-      <c r="AT7" s="63" t="n">
+      <c r="AS7" s="82"/>
+      <c r="AT7" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" s="63" t="n">
+      <c r="AU7" s="64" t="n">
         <v>-1</v>
       </c>
-      <c r="AV7" s="63" t="n">
+      <c r="AV7" s="64" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AW7" s="81"/>
-      <c r="AX7" s="47" t="n">
+      <c r="AW7" s="82"/>
+      <c r="AX7" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" s="47" t="n">
+      <c r="AY7" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ7" s="47" t="n">
+      <c r="AZ7" s="48" t="n">
         <v>-1.5</v>
       </c>
-      <c r="BA7" s="64" t="s">
+      <c r="BA7" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="BB7" s="64" t="s">
+      <c r="BB7" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="BC7" s="64" t="s">
+      <c r="BC7" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="BD7" s="81"/>
-      <c r="BE7" s="65" t="s">
+      <c r="BD7" s="82"/>
+      <c r="BE7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="BF7" s="65" t="s">
+      <c r="BF7" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="BG7" s="65" t="s">
+      <c r="BG7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="BH7" s="81"/>
-      <c r="BI7" s="82" t="s">
+      <c r="BH7" s="82"/>
+      <c r="BI7" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="BJ7" s="82" t="s">
+      <c r="BJ7" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="BK7" s="82" t="s">
+      <c r="BK7" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="BL7" s="81"/>
-      <c r="BM7" s="48" t="s">
+      <c r="BL7" s="82"/>
+      <c r="BM7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="BN7" s="49" t="s">
+      <c r="BN7" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="81"/>
-      <c r="BP7" s="30"/>
+      <c r="BO7" s="82"/>
+      <c r="BP7" s="31"/>
     </row>
-    <row r="8" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="66" t="s">
+      <c r="H8" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="66" t="s">
+      <c r="I8" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="66" t="s">
+      <c r="J8" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="66" t="s">
+      <c r="K8" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="66" t="s">
+      <c r="L8" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="66" t="s">
+      <c r="M8" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="66" t="s">
+      <c r="N8" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="66" t="s">
+      <c r="O8" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="66" t="s">
+      <c r="Q8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="66" t="s">
+      <c r="R8" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="66" t="s">
+      <c r="S8" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="T8" s="66" t="s">
+      <c r="T8" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="66" t="s">
+      <c r="U8" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="66" t="s">
+      <c r="V8" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="66" t="s">
+      <c r="W8" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="66" t="s">
+      <c r="X8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="Z8" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="AA8" s="66" t="s">
+      <c r="AA8" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AB8" s="66" t="s">
+      <c r="AB8" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="AC8" s="66" t="s">
+      <c r="AC8" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AD8" s="66" t="s">
+      <c r="AD8" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AE8" s="66" t="s">
+      <c r="AE8" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="AF8" s="66" t="s">
+      <c r="AF8" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="66" t="s">
+      <c r="AG8" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="AH8" s="66" t="s">
+      <c r="AH8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="66" t="s">
+      <c r="AI8" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="AJ8" s="66" t="s">
+      <c r="AJ8" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="AK8" s="66" t="s">
+      <c r="AK8" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="AL8" s="66" t="s">
+      <c r="AL8" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="AM8" s="66" t="s">
+      <c r="AM8" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="AN8" s="66" t="s">
+      <c r="AN8" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="AO8" s="66" t="s">
+      <c r="AO8" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="AP8" s="66" t="s">
+      <c r="AP8" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="AQ8" s="66" t="s">
+      <c r="AQ8" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="AR8" s="66" t="s">
+      <c r="AR8" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="AS8" s="66" t="s">
+      <c r="AS8" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="AT8" s="66" t="s">
+      <c r="AT8" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="AU8" s="66" t="s">
+      <c r="AU8" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="AV8" s="66" t="s">
+      <c r="AV8" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="AW8" s="66" t="s">
+      <c r="AW8" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AX8" s="66" t="s">
+      <c r="AX8" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="AY8" s="66" t="s">
+      <c r="AY8" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="AZ8" s="66" t="s">
+      <c r="AZ8" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="BA8" s="66" t="s">
+      <c r="BA8" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="BB8" s="66" t="s">
+      <c r="BB8" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="BC8" s="66" t="s">
+      <c r="BC8" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="BD8" s="66" t="s">
+      <c r="BD8" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="BE8" s="66" t="s">
+      <c r="BE8" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="BF8" s="66" t="s">
+      <c r="BF8" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="BG8" s="66" t="s">
+      <c r="BG8" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="BH8" s="66" t="s">
+      <c r="BH8" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="BI8" s="66" t="s">
+      <c r="BI8" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="BJ8" s="66" t="s">
+      <c r="BJ8" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="BK8" s="66" t="s">
+      <c r="BK8" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="BL8" s="66" t="s">
+      <c r="BL8" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="BM8" s="66" t="s">
+      <c r="BM8" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="BN8" s="66" t="s">
+      <c r="BN8" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="BO8" s="66" t="s">
+      <c r="BO8" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="BP8" s="66" t="s">
+      <c r="BP8" s="67" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="B2:H3"/>
@@ -4817,844 +4909,844 @@
   <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="50" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="53" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="150.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="33" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="40" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="45" min="45" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="49" min="49" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="50" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="67" min="53" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="150.71"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="7" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="54" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="15" t="s">
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="68" t="s">
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-      <c r="AA5" s="16" t="s">
+      <c r="Y5" s="69"/>
+      <c r="Z5" s="69"/>
+      <c r="AA5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="69" t="s">
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="AD5" s="69"/>
-      <c r="AE5" s="17" t="s">
+      <c r="AD5" s="70"/>
+      <c r="AE5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="18" t="s">
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="AH5" s="19" t="s">
+      <c r="AH5" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="19"/>
-      <c r="AK5" s="20" t="s">
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="16" t="s">
+      <c r="AL5" s="21"/>
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="21" t="s">
+      <c r="AO5" s="17"/>
+      <c r="AP5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AQ5" s="22" t="s">
+      <c r="AQ5" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AR5" s="22"/>
-      <c r="AS5" s="70" t="s">
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="23" t="s">
+      <c r="AT5" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="70" t="s">
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="AX5" s="24" t="s">
+      <c r="AX5" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="AY5" s="24"/>
-      <c r="AZ5" s="24"/>
-      <c r="BA5" s="27" t="s">
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="70" t="s">
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="BE5" s="28" t="s">
+      <c r="BE5" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="70" t="s">
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="BI5" s="71" t="s">
+      <c r="BI5" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="BJ5" s="71"/>
-      <c r="BK5" s="71"/>
-      <c r="BL5" s="70" t="s">
+      <c r="BJ5" s="72"/>
+      <c r="BK5" s="72"/>
+      <c r="BL5" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="BM5" s="25" t="s">
+      <c r="BM5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="BN5" s="25"/>
-      <c r="BO5" s="70" t="s">
+      <c r="BN5" s="26"/>
+      <c r="BO5" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="BP5" s="30" t="s">
+      <c r="BP5" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="32" t="n">
+    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="33" t="n">
+      <c r="J6" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="35" t="n">
+      <c r="Q6" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="35" t="n">
+      <c r="R6" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="35" t="n">
+      <c r="S6" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="T6" s="35" t="n">
+      <c r="T6" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="38" t="n">
+      <c r="U6" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="38" t="n">
+      <c r="V6" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="W6" s="38" t="n">
+      <c r="W6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="X6" s="72" t="n">
+      <c r="X6" s="73" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="72" t="n">
+      <c r="Y6" s="73" t="n">
         <v>43</v>
       </c>
-      <c r="Z6" s="72" t="n">
+      <c r="Z6" s="73" t="n">
         <v>29</v>
       </c>
-      <c r="AA6" s="39" t="n">
+      <c r="AA6" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="AB6" s="39" t="n">
+      <c r="AB6" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="AC6" s="73" t="n">
+      <c r="AC6" s="74" t="n">
         <v>25</v>
       </c>
-      <c r="AD6" s="73" t="n">
+      <c r="AD6" s="74" t="n">
         <v>26</v>
       </c>
-      <c r="AE6" s="40" t="n">
+      <c r="AE6" s="41" t="n">
         <v>27</v>
       </c>
-      <c r="AF6" s="40" t="n">
+      <c r="AF6" s="41" t="n">
         <v>28</v>
       </c>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="41" t="n">
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="AI6" s="41" t="n">
+      <c r="AI6" s="42" t="n">
         <v>31</v>
       </c>
-      <c r="AJ6" s="41" t="n">
+      <c r="AJ6" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="AK6" s="42" t="n">
+      <c r="AK6" s="43" t="n">
         <v>45</v>
       </c>
-      <c r="AL6" s="42" t="n">
+      <c r="AL6" s="43" t="n">
         <v>46</v>
       </c>
-      <c r="AM6" s="42" t="n">
+      <c r="AM6" s="43" t="n">
         <v>47</v>
       </c>
-      <c r="AN6" s="39" t="n">
+      <c r="AN6" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="AO6" s="39" t="n">
+      <c r="AO6" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="AP6" s="43" t="n">
+      <c r="AP6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="AQ6" s="44" t="n">
+      <c r="AQ6" s="45" t="n">
         <v>48</v>
       </c>
-      <c r="AR6" s="44" t="n">
+      <c r="AR6" s="45" t="n">
         <v>49</v>
       </c>
-      <c r="AS6" s="74" t="n">
+      <c r="AS6" s="75" t="n">
         <v>36</v>
       </c>
-      <c r="AT6" s="45" t="n">
+      <c r="AT6" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="AU6" s="45" t="n">
+      <c r="AU6" s="46" t="n">
         <v>51</v>
       </c>
-      <c r="AV6" s="45" t="n">
+      <c r="AV6" s="46" t="n">
         <v>52</v>
       </c>
-      <c r="AW6" s="74" t="n">
+      <c r="AW6" s="75" t="n">
         <v>37</v>
       </c>
-      <c r="AX6" s="75" t="n">
+      <c r="AX6" s="76" t="n">
         <v>53</v>
       </c>
-      <c r="AY6" s="75" t="n">
+      <c r="AY6" s="76" t="n">
         <v>54</v>
       </c>
-      <c r="AZ6" s="75" t="n">
+      <c r="AZ6" s="76" t="n">
         <v>55</v>
       </c>
-      <c r="BA6" s="51" t="n">
+      <c r="BA6" s="52" t="n">
         <v>56</v>
       </c>
-      <c r="BB6" s="51" t="n">
+      <c r="BB6" s="52" t="n">
         <v>57</v>
       </c>
-      <c r="BC6" s="51" t="n">
+      <c r="BC6" s="52" t="n">
         <v>58</v>
       </c>
-      <c r="BD6" s="74" t="n">
+      <c r="BD6" s="75" t="n">
         <v>137</v>
       </c>
-      <c r="BE6" s="52" t="n">
+      <c r="BE6" s="53" t="n">
         <v>59</v>
       </c>
-      <c r="BF6" s="52" t="n">
+      <c r="BF6" s="53" t="n">
         <v>60</v>
       </c>
-      <c r="BG6" s="52" t="n">
+      <c r="BG6" s="53" t="n">
         <v>61</v>
       </c>
-      <c r="BH6" s="74" t="n">
+      <c r="BH6" s="75" t="n">
         <v>138</v>
       </c>
-      <c r="BI6" s="76" t="n">
+      <c r="BI6" s="77" t="n">
         <v>62</v>
       </c>
-      <c r="BJ6" s="76" t="n">
+      <c r="BJ6" s="77" t="n">
         <v>63</v>
       </c>
-      <c r="BK6" s="76" t="n">
+      <c r="BK6" s="77" t="n">
         <v>64</v>
       </c>
-      <c r="BL6" s="74" t="n">
+      <c r="BL6" s="75" t="n">
         <v>139</v>
       </c>
-      <c r="BM6" s="48" t="n">
+      <c r="BM6" s="49" t="n">
         <v>65</v>
       </c>
-      <c r="BN6" s="49" t="n">
+      <c r="BN6" s="50" t="n">
         <v>66</v>
       </c>
-      <c r="BO6" s="74" t="n">
+      <c r="BO6" s="75" t="n">
         <v>38</v>
       </c>
-      <c r="BP6" s="30"/>
+      <c r="BP6" s="31"/>
     </row>
-    <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="77" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77" t="s">
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77" t="s">
+      <c r="R7" s="78"/>
+      <c r="S7" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="T7" s="77"/>
-      <c r="U7" s="57" t="s">
+      <c r="T7" s="78"/>
+      <c r="U7" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="V7" s="57"/>
-      <c r="W7" s="57" t="s">
+      <c r="V7" s="58"/>
+      <c r="W7" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="X7" s="78" t="s">
+      <c r="X7" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="Y7" s="78" t="s">
+      <c r="Y7" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="Z7" s="78" t="s">
+      <c r="Z7" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="AA7" s="58" t="s">
+      <c r="AA7" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="58" t="s">
+      <c r="AB7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="AC7" s="79" t="s">
+      <c r="AC7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="79" t="s">
+      <c r="AD7" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="59" t="s">
+      <c r="AE7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="59" t="s">
+      <c r="AF7" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="60" t="s">
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="AI7" s="60" t="s">
+      <c r="AI7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AJ7" s="60" t="s">
+      <c r="AJ7" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AK7" s="61" t="s">
+      <c r="AK7" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="AL7" s="61" t="s">
+      <c r="AL7" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="AM7" s="61" t="s">
+      <c r="AM7" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="AN7" s="58" t="s">
+      <c r="AN7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="58" t="s">
+      <c r="AO7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AP7" s="80"/>
-      <c r="AQ7" s="62" t="s">
+      <c r="AP7" s="81"/>
+      <c r="AQ7" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AR7" s="62" t="s">
+      <c r="AR7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="AS7" s="81"/>
-      <c r="AT7" s="63" t="n">
+      <c r="AS7" s="82"/>
+      <c r="AT7" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" s="63" t="n">
+      <c r="AU7" s="64" t="n">
         <v>-1</v>
       </c>
-      <c r="AV7" s="63" t="n">
+      <c r="AV7" s="64" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AW7" s="81"/>
-      <c r="AX7" s="47" t="n">
+      <c r="AW7" s="82"/>
+      <c r="AX7" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" s="47" t="n">
+      <c r="AY7" s="48" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ7" s="47" t="n">
+      <c r="AZ7" s="48" t="n">
         <v>-1.5</v>
       </c>
-      <c r="BA7" s="64" t="s">
+      <c r="BA7" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="BB7" s="64" t="s">
+      <c r="BB7" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="BC7" s="64" t="s">
+      <c r="BC7" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="BD7" s="81"/>
-      <c r="BE7" s="65" t="s">
+      <c r="BD7" s="82"/>
+      <c r="BE7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="BF7" s="65" t="s">
+      <c r="BF7" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="BG7" s="65" t="s">
+      <c r="BG7" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="BH7" s="81"/>
-      <c r="BI7" s="82" t="s">
+      <c r="BH7" s="82"/>
+      <c r="BI7" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="BJ7" s="82" t="s">
+      <c r="BJ7" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="BK7" s="82" t="s">
+      <c r="BK7" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="BL7" s="81"/>
-      <c r="BM7" s="48" t="s">
+      <c r="BL7" s="82"/>
+      <c r="BM7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="BN7" s="49" t="s">
+      <c r="BN7" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="81"/>
-      <c r="BP7" s="30"/>
+      <c r="BO7" s="82"/>
+      <c r="BP7" s="31"/>
     </row>
-    <row r="8" s="67" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+    <row r="8" s="68" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="66" t="s">
+      <c r="H8" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="66" t="s">
+      <c r="I8" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="66" t="s">
+      <c r="J8" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="66" t="s">
+      <c r="K8" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="66" t="s">
+      <c r="L8" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="66" t="s">
+      <c r="M8" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="66" t="s">
+      <c r="N8" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="66" t="s">
+      <c r="O8" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="66" t="s">
+      <c r="Q8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="66" t="s">
+      <c r="R8" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="66" t="s">
+      <c r="S8" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="T8" s="66" t="s">
+      <c r="T8" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="66" t="s">
+      <c r="U8" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="66" t="s">
+      <c r="V8" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="66" t="s">
+      <c r="W8" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="66" t="s">
+      <c r="X8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="Z8" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="AA8" s="66" t="s">
+      <c r="AA8" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AB8" s="66" t="s">
+      <c r="AB8" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="AC8" s="66" t="s">
+      <c r="AC8" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AD8" s="66" t="s">
+      <c r="AD8" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AE8" s="66" t="s">
+      <c r="AE8" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="AF8" s="66" t="s">
+      <c r="AF8" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="AG8" s="66" t="s">
+      <c r="AG8" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="AH8" s="66" t="s">
+      <c r="AH8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AI8" s="66" t="s">
+      <c r="AI8" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="AJ8" s="66" t="s">
+      <c r="AJ8" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="AK8" s="66" t="s">
+      <c r="AK8" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="AL8" s="66" t="s">
+      <c r="AL8" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="AM8" s="66" t="s">
+      <c r="AM8" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="AN8" s="66" t="s">
+      <c r="AN8" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="AO8" s="66" t="s">
+      <c r="AO8" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="AP8" s="66" t="s">
+      <c r="AP8" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="AQ8" s="66" t="s">
+      <c r="AQ8" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="AR8" s="66" t="s">
+      <c r="AR8" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="AS8" s="66" t="s">
+      <c r="AS8" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="AT8" s="66" t="s">
+      <c r="AT8" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="AU8" s="66" t="s">
+      <c r="AU8" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="AV8" s="66" t="s">
+      <c r="AV8" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="AW8" s="66" t="s">
+      <c r="AW8" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AX8" s="66" t="s">
+      <c r="AX8" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="AY8" s="66" t="s">
+      <c r="AY8" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="AZ8" s="66" t="s">
+      <c r="AZ8" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="BA8" s="66" t="s">
+      <c r="BA8" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="BB8" s="66" t="s">
+      <c r="BB8" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="BC8" s="66" t="s">
+      <c r="BC8" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="BD8" s="66" t="s">
+      <c r="BD8" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="BE8" s="66" t="s">
+      <c r="BE8" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="BF8" s="66" t="s">
+      <c r="BF8" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="BG8" s="66" t="s">
+      <c r="BG8" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="BH8" s="66" t="s">
+      <c r="BH8" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="BI8" s="66" t="s">
+      <c r="BI8" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="BJ8" s="66" t="s">
+      <c r="BJ8" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="BK8" s="66" t="s">
+      <c r="BK8" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="BL8" s="66" t="s">
+      <c r="BL8" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="BM8" s="66" t="s">
+      <c r="BM8" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="BN8" s="66" t="s">
+      <c r="BN8" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="BO8" s="66" t="s">
+      <c r="BO8" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="BP8" s="66" t="s">
+      <c r="BP8" s="67" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="1"/>
-      <c r="AR9" s="1"/>
-      <c r="AS9" s="1"/>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
-      <c r="AW9" s="1"/>
-      <c r="AX9" s="1"/>
-      <c r="AY9" s="1"/>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
-      <c r="BC9" s="1"/>
-      <c r="BD9" s="1"/>
-      <c r="BE9" s="1"/>
-      <c r="BF9" s="1"/>
-      <c r="BG9" s="1"/>
-      <c r="BH9" s="1"/>
-      <c r="BI9" s="1"/>
-      <c r="BJ9" s="1"/>
-      <c r="BK9" s="1"/>
-      <c r="BL9" s="1"/>
-      <c r="BM9" s="1"/>
-      <c r="BN9" s="1"/>
-      <c r="BO9" s="1"/>
-      <c r="BP9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
+      <c r="AU9" s="2"/>
+      <c r="AV9" s="2"/>
+      <c r="AW9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="AY9" s="2"/>
+      <c r="AZ9" s="2"/>
+      <c r="BA9" s="2"/>
+      <c r="BB9" s="2"/>
+      <c r="BC9" s="2"/>
+      <c r="BD9" s="2"/>
+      <c r="BE9" s="2"/>
+      <c r="BF9" s="2"/>
+      <c r="BG9" s="2"/>
+      <c r="BH9" s="2"/>
+      <c r="BI9" s="2"/>
+      <c r="BJ9" s="2"/>
+      <c r="BK9" s="2"/>
+      <c r="BL9" s="2"/>
+      <c r="BM9" s="2"/>
+      <c r="BN9" s="2"/>
+      <c r="BO9" s="2"/>
+      <c r="BP9" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -5706,746 +5798,746 @@
   <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="22" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="26" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="32" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="38" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="39" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="55" min="55" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="56" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="59" min="58" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="60" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="0" width="150.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="22" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="26" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="32" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="38" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="39" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="55" min="55" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="56" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="59" min="58" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="60" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="150.71"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
     </row>
-    <row r="5" s="6" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="7" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="83" t="s">
+      <c r="K5" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="54" t="s">
+      <c r="L5" s="84"/>
+      <c r="M5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="84" t="s">
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="85" t="s">
         <v>168</v>
       </c>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="18" t="s">
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="85" t="s">
+      <c r="W5" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="85"/>
-      <c r="Y5" s="85"/>
-      <c r="Z5" s="16" t="s">
+      <c r="X5" s="86"/>
+      <c r="Y5" s="86"/>
+      <c r="Z5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AA5" s="16"/>
-      <c r="AB5" s="21" t="s">
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AC5" s="86" t="s">
+      <c r="AC5" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AD5" s="86"/>
-      <c r="AE5" s="16" t="s">
+      <c r="AD5" s="87"/>
+      <c r="AE5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="17" t="s">
+      <c r="AF5" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="17"/>
-      <c r="AL5" s="16" t="s">
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18"/>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="AM5" s="12" t="s">
+      <c r="AM5" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="87" t="s">
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="13"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="AR5" s="87"/>
-      <c r="AS5" s="87"/>
-      <c r="AT5" s="87"/>
-      <c r="AU5" s="12" t="s">
+      <c r="AR5" s="88"/>
+      <c r="AS5" s="88"/>
+      <c r="AT5" s="88"/>
+      <c r="AU5" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="17" t="s">
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="13"/>
+      <c r="AY5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="AZ5" s="17"/>
-      <c r="BA5" s="17"/>
-      <c r="BB5" s="17"/>
-      <c r="BC5" s="16" t="s">
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="BD5" s="70" t="s">
+      <c r="BD5" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="BE5" s="70"/>
-      <c r="BF5" s="70"/>
-      <c r="BG5" s="70"/>
-      <c r="BH5" s="88" t="s">
+      <c r="BE5" s="71"/>
+      <c r="BF5" s="71"/>
+      <c r="BG5" s="71"/>
+      <c r="BH5" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="BI5" s="88"/>
-      <c r="BJ5" s="70" t="s">
+      <c r="BI5" s="89"/>
+      <c r="BJ5" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="BK5" s="70"/>
-      <c r="BL5" s="88" t="s">
+      <c r="BK5" s="71"/>
+      <c r="BL5" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="BM5" s="88"/>
-      <c r="BN5" s="30" t="s">
+      <c r="BM5" s="89"/>
+      <c r="BN5" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11" t="n">
+    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="89" t="n">
+      <c r="K6" s="90" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="89" t="n">
+      <c r="L6" s="90" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="35" t="n">
+      <c r="Q6" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="35" t="n">
+      <c r="R6" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="90" t="n">
+      <c r="S6" s="91" t="n">
         <v>76</v>
       </c>
-      <c r="T6" s="90" t="n">
+      <c r="T6" s="91" t="n">
         <v>77</v>
       </c>
-      <c r="U6" s="90" t="n">
+      <c r="U6" s="91" t="n">
         <v>78</v>
       </c>
-      <c r="V6" s="18"/>
-      <c r="W6" s="91" t="n">
+      <c r="V6" s="19"/>
+      <c r="W6" s="92" t="n">
         <v>32</v>
       </c>
-      <c r="X6" s="91" t="n">
+      <c r="X6" s="92" t="n">
         <v>33</v>
       </c>
-      <c r="Y6" s="91" t="n">
+      <c r="Y6" s="92" t="n">
         <v>34</v>
       </c>
-      <c r="Z6" s="16" t="n">
+      <c r="Z6" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="AA6" s="16" t="n">
+      <c r="AA6" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="AB6" s="21" t="n">
+      <c r="AB6" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="AC6" s="92" t="n">
+      <c r="AC6" s="93" t="n">
         <v>38</v>
       </c>
-      <c r="AD6" s="92" t="n">
+      <c r="AD6" s="93" t="n">
         <v>39</v>
       </c>
-      <c r="AE6" s="16" t="n">
+      <c r="AE6" s="17" t="n">
         <v>127</v>
       </c>
-      <c r="AF6" s="59" t="n">
+      <c r="AF6" s="60" t="n">
         <v>91</v>
       </c>
-      <c r="AG6" s="59" t="n">
+      <c r="AG6" s="60" t="n">
         <v>92</v>
       </c>
-      <c r="AH6" s="59" t="n">
+      <c r="AH6" s="60" t="n">
         <v>93</v>
       </c>
-      <c r="AI6" s="93" t="n">
+      <c r="AI6" s="94" t="n">
         <v>94</v>
       </c>
-      <c r="AJ6" s="93" t="n">
+      <c r="AJ6" s="94" t="n">
         <v>95</v>
       </c>
-      <c r="AK6" s="93" t="n">
+      <c r="AK6" s="94" t="n">
         <v>96</v>
       </c>
-      <c r="AL6" s="16" t="n">
+      <c r="AL6" s="17" t="n">
         <v>129</v>
       </c>
-      <c r="AM6" s="53" t="n">
+      <c r="AM6" s="54" t="n">
         <v>97</v>
       </c>
-      <c r="AN6" s="53" t="n">
+      <c r="AN6" s="54" t="n">
         <v>98</v>
       </c>
-      <c r="AO6" s="93" t="n">
+      <c r="AO6" s="94" t="n">
         <v>99</v>
       </c>
-      <c r="AP6" s="93" t="n">
+      <c r="AP6" s="94" t="n">
         <v>100</v>
       </c>
-      <c r="AQ6" s="59" t="n">
+      <c r="AQ6" s="60" t="n">
         <v>101</v>
       </c>
-      <c r="AR6" s="59" t="n">
+      <c r="AR6" s="60" t="n">
         <v>102</v>
       </c>
-      <c r="AS6" s="93" t="n">
+      <c r="AS6" s="94" t="n">
         <v>103</v>
       </c>
-      <c r="AT6" s="94" t="n">
+      <c r="AT6" s="95" t="n">
         <v>104</v>
       </c>
-      <c r="AU6" s="53" t="n">
+      <c r="AU6" s="54" t="n">
         <v>105</v>
       </c>
-      <c r="AV6" s="53" t="n">
+      <c r="AV6" s="54" t="n">
         <v>106</v>
       </c>
-      <c r="AW6" s="93" t="n">
+      <c r="AW6" s="94" t="n">
         <v>107</v>
       </c>
-      <c r="AX6" s="93" t="n">
+      <c r="AX6" s="94" t="n">
         <v>108</v>
       </c>
-      <c r="AY6" s="59" t="n">
+      <c r="AY6" s="60" t="n">
         <v>109</v>
       </c>
-      <c r="AZ6" s="59" t="n">
+      <c r="AZ6" s="60" t="n">
         <v>110</v>
       </c>
-      <c r="BA6" s="93" t="n">
+      <c r="BA6" s="94" t="n">
         <v>111</v>
       </c>
-      <c r="BB6" s="93" t="n">
+      <c r="BB6" s="94" t="n">
         <v>112</v>
       </c>
-      <c r="BC6" s="16" t="n">
+      <c r="BC6" s="17" t="n">
         <v>128</v>
       </c>
-      <c r="BD6" s="95" t="n">
+      <c r="BD6" s="96" t="n">
         <v>113</v>
       </c>
-      <c r="BE6" s="95" t="n">
+      <c r="BE6" s="96" t="n">
         <v>114</v>
       </c>
-      <c r="BF6" s="81" t="n">
+      <c r="BF6" s="82" t="n">
         <v>115</v>
       </c>
-      <c r="BG6" s="81" t="n">
+      <c r="BG6" s="82" t="n">
         <v>116</v>
       </c>
-      <c r="BH6" s="95" t="n">
+      <c r="BH6" s="96" t="n">
         <v>117</v>
       </c>
-      <c r="BI6" s="95" t="n">
+      <c r="BI6" s="96" t="n">
         <v>118</v>
       </c>
-      <c r="BJ6" s="81" t="n">
+      <c r="BJ6" s="82" t="n">
         <v>119</v>
       </c>
-      <c r="BK6" s="81" t="n">
+      <c r="BK6" s="82" t="n">
         <v>120</v>
       </c>
-      <c r="BL6" s="95" t="n">
+      <c r="BL6" s="96" t="n">
         <v>121</v>
       </c>
-      <c r="BM6" s="95" t="n">
+      <c r="BM6" s="96" t="n">
         <v>122</v>
       </c>
-      <c r="BN6" s="30"/>
+      <c r="BN6" s="31"/>
     </row>
-    <row r="7" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="89" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="89" t="s">
+      <c r="L7" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="77" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77" t="s">
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="77"/>
-      <c r="S7" s="90" t="s">
+      <c r="R7" s="78"/>
+      <c r="S7" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="90" t="s">
+      <c r="T7" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="90" t="s">
+      <c r="U7" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="V7" s="18"/>
-      <c r="W7" s="91" t="s">
+      <c r="V7" s="19"/>
+      <c r="W7" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="X7" s="91" t="s">
+      <c r="X7" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="Y7" s="91" t="s">
+      <c r="Y7" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="Z7" s="58" t="s">
+      <c r="Z7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AA7" s="58" t="s">
+      <c r="AA7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="92" t="s">
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="92" t="s">
+      <c r="AD7" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="AE7" s="16"/>
-      <c r="AF7" s="59" t="s">
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="AG7" s="59" t="s">
+      <c r="AG7" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="AH7" s="59" t="s">
+      <c r="AH7" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="AI7" s="93" t="s">
+      <c r="AI7" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="AJ7" s="93" t="s">
+      <c r="AJ7" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="AK7" s="93" t="s">
+      <c r="AK7" s="94" t="s">
         <v>185</v>
       </c>
-      <c r="AL7" s="58"/>
-      <c r="AM7" s="53" t="s">
+      <c r="AL7" s="59"/>
+      <c r="AM7" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="AN7" s="53" t="s">
+      <c r="AN7" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="AO7" s="93" t="s">
+      <c r="AO7" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="AP7" s="93" t="s">
+      <c r="AP7" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="AQ7" s="59" t="s">
+      <c r="AQ7" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="AR7" s="59" t="s">
+      <c r="AR7" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="AS7" s="93" t="s">
+      <c r="AS7" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="AT7" s="94" t="s">
+      <c r="AT7" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="AU7" s="96" t="s">
+      <c r="AU7" s="97" t="s">
         <v>188</v>
       </c>
-      <c r="AV7" s="96" t="s">
+      <c r="AV7" s="97" t="s">
         <v>180</v>
       </c>
-      <c r="AW7" s="93" t="s">
+      <c r="AW7" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="AX7" s="93" t="s">
+      <c r="AX7" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="AY7" s="59" t="s">
+      <c r="AY7" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="AZ7" s="59" t="s">
+      <c r="AZ7" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="BA7" s="93" t="s">
+      <c r="BA7" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="BB7" s="93" t="s">
+      <c r="BB7" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="BC7" s="16"/>
-      <c r="BD7" s="95" t="s">
+      <c r="BC7" s="17"/>
+      <c r="BD7" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="BE7" s="95" t="s">
+      <c r="BE7" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="BF7" s="81" t="s">
+      <c r="BF7" s="82" t="s">
         <v>190</v>
       </c>
-      <c r="BG7" s="81" t="s">
+      <c r="BG7" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="BH7" s="97" t="s">
+      <c r="BH7" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="BI7" s="97" t="s">
+      <c r="BI7" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="BJ7" s="81" t="s">
+      <c r="BJ7" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="BK7" s="81" t="s">
+      <c r="BK7" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="BL7" s="97" t="s">
+      <c r="BL7" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="BM7" s="97" t="s">
+      <c r="BM7" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="BN7" s="30"/>
+      <c r="BN7" s="31"/>
     </row>
-    <row r="8" s="67" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="67" t="s">
+    <row r="8" s="68" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="67" t="s">
+      <c r="I8" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="67" t="s">
+      <c r="J8" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="67" t="s">
+      <c r="K8" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="67" t="s">
+      <c r="L8" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="67" t="s">
+      <c r="M8" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="67" t="s">
+      <c r="N8" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="67" t="s">
+      <c r="O8" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="67" t="s">
+      <c r="P8" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="67" t="s">
+      <c r="Q8" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="67" t="s">
+      <c r="R8" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="67" t="s">
+      <c r="S8" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="T8" s="67" t="s">
+      <c r="T8" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="U8" s="67" t="s">
+      <c r="U8" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="V8" s="67" t="s">
+      <c r="V8" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="W8" s="67" t="s">
+      <c r="W8" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="X8" s="67" t="s">
+      <c r="X8" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="Y8" s="67" t="s">
+      <c r="Y8" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="Z8" s="67" t="s">
+      <c r="Z8" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="AA8" s="67" t="s">
+      <c r="AA8" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="AB8" s="67" t="s">
+      <c r="AB8" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="AC8" s="67" t="s">
+      <c r="AC8" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="AD8" s="67" t="s">
+      <c r="AD8" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="AE8" s="67" t="s">
+      <c r="AE8" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="AF8" s="67" t="s">
+      <c r="AF8" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="AG8" s="67" t="s">
+      <c r="AG8" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="AH8" s="67" t="s">
+      <c r="AH8" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="AI8" s="67" t="s">
+      <c r="AI8" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="AJ8" s="67" t="s">
+      <c r="AJ8" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="AK8" s="67" t="s">
+      <c r="AK8" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="AL8" s="67" t="s">
+      <c r="AL8" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="AM8" s="67" t="s">
+      <c r="AM8" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="AN8" s="67" t="s">
+      <c r="AN8" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="AO8" s="67" t="s">
+      <c r="AO8" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="AP8" s="67" t="s">
+      <c r="AP8" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="AQ8" s="67" t="s">
+      <c r="AQ8" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="AR8" s="67" t="s">
+      <c r="AR8" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="AS8" s="67" t="s">
+      <c r="AS8" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="AT8" s="67" t="s">
+      <c r="AT8" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="AU8" s="67" t="s">
+      <c r="AU8" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="AV8" s="67" t="s">
+      <c r="AV8" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="AW8" s="67" t="s">
+      <c r="AW8" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="AX8" s="67" t="s">
+      <c r="AX8" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="AY8" s="67" t="s">
+      <c r="AY8" s="68" t="s">
         <v>211</v>
       </c>
-      <c r="AZ8" s="67" t="s">
+      <c r="AZ8" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="BA8" s="67" t="s">
+      <c r="BA8" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="BB8" s="67" t="s">
+      <c r="BB8" s="68" t="s">
         <v>214</v>
       </c>
-      <c r="BC8" s="67" t="s">
+      <c r="BC8" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="BD8" s="67" t="s">
+      <c r="BD8" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="BE8" s="67" t="s">
+      <c r="BE8" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="BF8" s="67" t="s">
+      <c r="BF8" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="BG8" s="67" t="s">
+      <c r="BG8" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="BH8" s="67" t="s">
+      <c r="BH8" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="BI8" s="67" t="s">
+      <c r="BI8" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="BJ8" s="67" t="s">
+      <c r="BJ8" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="BK8" s="67" t="s">
+      <c r="BK8" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="BL8" s="67" t="s">
+      <c r="BL8" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="BM8" s="67" t="s">
+      <c r="BM8" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="BN8" s="67" t="s">
+      <c r="BN8" s="68" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6495,691 +6587,691 @@
   <dimension ref="A1:BJ8"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="25" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="29" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="35" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="44" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="61" min="56" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="150.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="63" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="0" width="100.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="15" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="25" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="29" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="35" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="44" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="61" min="56" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="150.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="63" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="1" width="100.71"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+    <row r="3" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
-    <row r="4" s="6" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
     </row>
-    <row r="5" s="98" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" s="99" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="83" t="s">
+      <c r="K5" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="54" t="s">
+      <c r="L5" s="84"/>
+      <c r="M5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="68" t="s">
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="18" t="s">
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="69"/>
+      <c r="Y5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Z5" s="85" t="s">
+      <c r="Z5" s="86" t="s">
         <v>223</v>
       </c>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="16" t="s">
+      <c r="AA5" s="86"/>
+      <c r="AB5" s="86"/>
+      <c r="AC5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AD5" s="16"/>
-      <c r="AE5" s="21" t="s">
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AF5" s="92" t="s">
+      <c r="AF5" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="AG5" s="92"/>
-      <c r="AH5" s="16" t="s">
+      <c r="AG5" s="93"/>
+      <c r="AH5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AI5" s="99" t="s">
+      <c r="AI5" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="99"/>
-      <c r="AM5" s="99"/>
-      <c r="AN5" s="99"/>
-      <c r="AO5" s="99"/>
-      <c r="AP5" s="99"/>
-      <c r="AQ5" s="26" t="s">
+      <c r="AJ5" s="100"/>
+      <c r="AK5" s="100"/>
+      <c r="AL5" s="100"/>
+      <c r="AM5" s="100"/>
+      <c r="AN5" s="100"/>
+      <c r="AO5" s="100"/>
+      <c r="AP5" s="100"/>
+      <c r="AQ5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AR5" s="12" t="s">
+      <c r="AR5" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="17" t="s">
+      <c r="AS5" s="13"/>
+      <c r="AT5" s="13"/>
+      <c r="AU5" s="13"/>
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="AY5" s="17"/>
-      <c r="AZ5" s="17"/>
-      <c r="BA5" s="17"/>
-      <c r="BB5" s="17"/>
-      <c r="BC5" s="17"/>
-      <c r="BD5" s="99" t="s">
+      <c r="AY5" s="18"/>
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="18"/>
+      <c r="BD5" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="BE5" s="99"/>
-      <c r="BF5" s="99" t="s">
+      <c r="BE5" s="100"/>
+      <c r="BF5" s="100" t="s">
         <v>225</v>
       </c>
-      <c r="BG5" s="99"/>
-      <c r="BH5" s="99" t="s">
+      <c r="BG5" s="100"/>
+      <c r="BH5" s="100" t="s">
         <v>226</v>
       </c>
-      <c r="BI5" s="99"/>
-      <c r="BJ5" s="100" t="s">
+      <c r="BI5" s="100"/>
+      <c r="BJ5" s="101" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" s="98" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="101"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11" t="n">
+    <row r="6" s="99" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="102"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="89" t="n">
+      <c r="K6" s="90" t="n">
         <v>9</v>
       </c>
-      <c r="L6" s="89" t="n">
+      <c r="L6" s="90" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="35" t="n">
+      <c r="M6" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="P6" s="35" t="n">
+      <c r="P6" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" s="35" t="n">
+      <c r="Q6" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="R6" s="35" t="n">
+      <c r="R6" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="S6" s="35" t="n">
+      <c r="S6" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="T6" s="35" t="n">
+      <c r="T6" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="U6" s="72" t="n">
+      <c r="U6" s="73" t="n">
         <v>22</v>
       </c>
-      <c r="V6" s="72"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="102" t="n">
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="103" t="n">
         <v>45</v>
       </c>
-      <c r="AA6" s="102" t="n">
+      <c r="AA6" s="103" t="n">
         <v>46</v>
       </c>
-      <c r="AB6" s="102" t="n">
+      <c r="AB6" s="103" t="n">
         <v>47</v>
       </c>
-      <c r="AC6" s="39" t="n">
+      <c r="AC6" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="AD6" s="39" t="n">
+      <c r="AD6" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="AE6" s="43" t="n">
+      <c r="AE6" s="44" t="n">
         <v>41</v>
       </c>
-      <c r="AF6" s="103" t="n">
+      <c r="AF6" s="104" t="n">
         <v>50</v>
       </c>
-      <c r="AG6" s="103" t="n">
+      <c r="AG6" s="104" t="n">
         <v>53</v>
       </c>
-      <c r="AH6" s="39" t="n">
+      <c r="AH6" s="40" t="n">
         <v>37</v>
       </c>
-      <c r="AI6" s="104" t="n">
+      <c r="AI6" s="105" t="n">
         <v>107</v>
       </c>
-      <c r="AJ6" s="104" t="n">
+      <c r="AJ6" s="105" t="n">
         <v>108</v>
       </c>
-      <c r="AK6" s="104" t="n">
+      <c r="AK6" s="105" t="n">
         <v>109</v>
       </c>
-      <c r="AL6" s="104" t="n">
+      <c r="AL6" s="105" t="n">
         <v>110</v>
       </c>
-      <c r="AM6" s="105" t="n">
+      <c r="AM6" s="106" t="n">
         <v>111</v>
       </c>
-      <c r="AN6" s="105" t="n">
+      <c r="AN6" s="106" t="n">
         <v>112</v>
       </c>
-      <c r="AO6" s="105" t="n">
+      <c r="AO6" s="106" t="n">
         <v>113</v>
       </c>
-      <c r="AP6" s="105" t="n">
+      <c r="AP6" s="106" t="n">
         <v>114</v>
       </c>
-      <c r="AQ6" s="106" t="n">
+      <c r="AQ6" s="107" t="n">
         <v>38</v>
       </c>
-      <c r="AR6" s="104" t="n">
+      <c r="AR6" s="105" t="n">
         <v>115</v>
       </c>
-      <c r="AS6" s="104" t="n">
+      <c r="AS6" s="105" t="n">
         <v>116</v>
       </c>
-      <c r="AT6" s="104" t="n">
+      <c r="AT6" s="105" t="n">
         <v>117</v>
       </c>
-      <c r="AU6" s="105" t="n">
+      <c r="AU6" s="106" t="n">
         <v>118</v>
       </c>
-      <c r="AV6" s="105" t="n">
+      <c r="AV6" s="106" t="n">
         <v>119</v>
       </c>
-      <c r="AW6" s="105" t="n">
+      <c r="AW6" s="106" t="n">
         <v>120</v>
       </c>
-      <c r="AX6" s="104" t="n">
+      <c r="AX6" s="105" t="n">
         <v>121</v>
       </c>
-      <c r="AY6" s="104" t="n">
+      <c r="AY6" s="105" t="n">
         <v>122</v>
       </c>
-      <c r="AZ6" s="104" t="n">
+      <c r="AZ6" s="105" t="n">
         <v>123</v>
       </c>
-      <c r="BA6" s="105" t="n">
+      <c r="BA6" s="106" t="n">
         <v>124</v>
       </c>
-      <c r="BB6" s="105" t="n">
+      <c r="BB6" s="106" t="n">
         <v>125</v>
       </c>
-      <c r="BC6" s="105" t="n">
+      <c r="BC6" s="106" t="n">
         <v>126</v>
       </c>
-      <c r="BD6" s="104" t="n">
+      <c r="BD6" s="105" t="n">
         <v>127</v>
       </c>
-      <c r="BE6" s="105" t="n">
+      <c r="BE6" s="106" t="n">
         <v>128</v>
       </c>
-      <c r="BF6" s="104" t="n">
+      <c r="BF6" s="105" t="n">
         <v>129</v>
       </c>
-      <c r="BG6" s="105" t="n">
+      <c r="BG6" s="106" t="n">
         <v>130</v>
       </c>
-      <c r="BH6" s="104" t="n">
+      <c r="BH6" s="105" t="n">
         <v>131</v>
       </c>
-      <c r="BI6" s="105" t="n">
+      <c r="BI6" s="106" t="n">
         <v>132</v>
       </c>
-      <c r="BJ6" s="100"/>
+      <c r="BJ6" s="101"/>
     </row>
-    <row r="7" s="98" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="49" t="s">
+    <row r="7" s="99" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="89" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="89" t="s">
+      <c r="L7" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="54" t="s">
+      <c r="M7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="77" t="s">
+      <c r="N7" s="55"/>
+      <c r="O7" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77" t="s">
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77" t="s">
+      <c r="R7" s="78"/>
+      <c r="S7" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="T7" s="77"/>
-      <c r="U7" s="78" t="s">
+      <c r="T7" s="78"/>
+      <c r="U7" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="V7" s="78" t="s">
+      <c r="V7" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="W7" s="78" t="s">
+      <c r="W7" s="79" t="s">
         <v>228</v>
       </c>
-      <c r="X7" s="78" t="s">
+      <c r="X7" s="79" t="s">
         <v>229</v>
       </c>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="91" t="s">
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="AA7" s="91" t="s">
+      <c r="AA7" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="AB7" s="91" t="s">
+      <c r="AB7" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="AC7" s="58" t="s">
+      <c r="AC7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="AD7" s="58" t="s">
+      <c r="AD7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="92" t="s">
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="AG7" s="92" t="s">
+      <c r="AG7" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="AH7" s="16"/>
-      <c r="AI7" s="104" t="s">
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="AJ7" s="104" t="s">
+      <c r="AJ7" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="AK7" s="104" t="s">
+      <c r="AK7" s="105" t="s">
         <v>231</v>
       </c>
-      <c r="AL7" s="104" t="s">
+      <c r="AL7" s="105" t="s">
         <v>232</v>
       </c>
-      <c r="AM7" s="105" t="s">
+      <c r="AM7" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="AN7" s="105" t="s">
+      <c r="AN7" s="106" t="s">
         <v>233</v>
       </c>
-      <c r="AO7" s="105" t="s">
+      <c r="AO7" s="106" t="s">
         <v>234</v>
       </c>
-      <c r="AP7" s="105" t="s">
+      <c r="AP7" s="106" t="s">
         <v>235</v>
       </c>
-      <c r="AQ7" s="107"/>
-      <c r="AR7" s="104" t="s">
+      <c r="AQ7" s="108"/>
+      <c r="AR7" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="AS7" s="104" t="s">
+      <c r="AS7" s="105" t="s">
         <v>181</v>
       </c>
-      <c r="AT7" s="104" t="s">
+      <c r="AT7" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="AU7" s="105" t="s">
+      <c r="AU7" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="AV7" s="105" t="s">
+      <c r="AV7" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="AW7" s="105" t="s">
+      <c r="AW7" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="AX7" s="104" t="s">
+      <c r="AX7" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="AY7" s="104" t="s">
+      <c r="AY7" s="105" t="s">
         <v>181</v>
       </c>
-      <c r="AZ7" s="104" t="s">
+      <c r="AZ7" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="BA7" s="105" t="s">
+      <c r="BA7" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="BB7" s="105" t="s">
+      <c r="BB7" s="106" t="s">
         <v>184</v>
       </c>
-      <c r="BC7" s="105" t="s">
+      <c r="BC7" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="BD7" s="104" t="s">
+      <c r="BD7" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="BE7" s="105" t="s">
+      <c r="BE7" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="BF7" s="104" t="s">
+      <c r="BF7" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="BG7" s="105" t="s">
+      <c r="BG7" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="BH7" s="104" t="s">
+      <c r="BH7" s="105" t="s">
         <v>180</v>
       </c>
-      <c r="BI7" s="105" t="s">
+      <c r="BI7" s="106" t="s">
         <v>183</v>
       </c>
-      <c r="BJ7" s="100"/>
+      <c r="BJ7" s="101"/>
     </row>
-    <row r="8" s="67" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="67" t="s">
+    <row r="8" s="68" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="67" t="s">
+      <c r="I8" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="67" t="s">
+      <c r="J8" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="67" t="s">
+      <c r="K8" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="67" t="s">
+      <c r="L8" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="67" t="s">
+      <c r="M8" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="67" t="s">
+      <c r="N8" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="O8" s="67" t="s">
+      <c r="O8" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="67" t="s">
+      <c r="P8" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="67" t="s">
+      <c r="Q8" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="67" t="s">
+      <c r="R8" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="S8" s="67" t="s">
+      <c r="S8" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="T8" s="67" t="s">
+      <c r="T8" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="67" t="s">
+      <c r="U8" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="V8" s="67" t="s">
+      <c r="V8" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="W8" s="67" t="s">
+      <c r="W8" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="X8" s="67" t="s">
+      <c r="X8" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="Y8" s="67" t="s">
+      <c r="Y8" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="Z8" s="67" t="s">
+      <c r="Z8" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="AA8" s="67" t="s">
+      <c r="AA8" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="67" t="s">
+      <c r="AB8" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="AC8" s="67" t="s">
+      <c r="AC8" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="AD8" s="67" t="s">
+      <c r="AD8" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="AE8" s="67" t="s">
+      <c r="AE8" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="AF8" s="67" t="s">
+      <c r="AF8" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="AG8" s="67" t="s">
+      <c r="AG8" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="AH8" s="67" t="s">
+      <c r="AH8" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="AI8" s="67" t="s">
+      <c r="AI8" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="AJ8" s="67" t="s">
+      <c r="AJ8" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="AK8" s="67" t="s">
+      <c r="AK8" s="68" t="s">
         <v>211</v>
       </c>
-      <c r="AL8" s="67" t="s">
+      <c r="AL8" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="AM8" s="67" t="s">
+      <c r="AM8" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="AN8" s="67" t="s">
+      <c r="AN8" s="68" t="s">
         <v>214</v>
       </c>
-      <c r="AO8" s="67" t="s">
+      <c r="AO8" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="AP8" s="67" t="s">
+      <c r="AP8" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AQ8" s="67" t="s">
+      <c r="AQ8" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="AR8" s="67" t="s">
+      <c r="AR8" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="AS8" s="67" t="s">
+      <c r="AS8" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="AT8" s="67" t="s">
+      <c r="AT8" s="68" t="s">
         <v>217</v>
       </c>
-      <c r="AU8" s="67" t="s">
+      <c r="AU8" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="AV8" s="67" t="s">
+      <c r="AV8" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="AW8" s="67" t="s">
+      <c r="AW8" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="AX8" s="67" t="s">
+      <c r="AX8" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="AY8" s="67" t="s">
+      <c r="AY8" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="AZ8" s="67" t="s">
+      <c r="AZ8" s="68" t="s">
         <v>237</v>
       </c>
-      <c r="BA8" s="67" t="s">
+      <c r="BA8" s="68" t="s">
         <v>238</v>
       </c>
-      <c r="BB8" s="67" t="s">
+      <c r="BB8" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="BC8" s="67" t="s">
+      <c r="BC8" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="BD8" s="67" t="s">
+      <c r="BD8" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="BE8" s="67" t="s">
+      <c r="BE8" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="BF8" s="67" t="s">
+      <c r="BF8" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="BG8" s="67" t="s">
+      <c r="BG8" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="BH8" s="67" t="s">
+      <c r="BH8" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="BI8" s="67" t="s">
+      <c r="BI8" s="68" t="s">
         <v>241</v>
       </c>
-      <c r="BJ8" s="67" t="s">
+      <c r="BJ8" s="68" t="s">
         <v>124</v>
       </c>
     </row>
@@ -7217,4 +7309,937 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BJ9"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="13" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="23" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="25" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="33" min="30" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="34" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="37" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="39" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="47" min="44" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="48" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="52" min="51" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="53" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="61" min="58" style="0" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="150.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="58" t="s">
+        <v>242</v>
+      </c>
+      <c r="U3" s="58"/>
+      <c r="V3" s="58"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="58"/>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="58"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="58"/>
+      <c r="AH3" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="58"/>
+      <c r="AK3" s="58"/>
+      <c r="AL3" s="58"/>
+      <c r="AM3" s="58"/>
+      <c r="AN3" s="58"/>
+      <c r="AO3" s="58"/>
+      <c r="AP3" s="58"/>
+      <c r="AQ3" s="58"/>
+      <c r="AR3" s="58"/>
+      <c r="AS3" s="58"/>
+      <c r="AT3" s="58"/>
+      <c r="AU3" s="58"/>
+      <c r="AV3" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW3" s="58"/>
+      <c r="AX3" s="58"/>
+      <c r="AY3" s="58"/>
+      <c r="AZ3" s="58"/>
+      <c r="BA3" s="58"/>
+      <c r="BB3" s="58"/>
+      <c r="BC3" s="58"/>
+      <c r="BD3" s="58"/>
+      <c r="BE3" s="58"/>
+      <c r="BF3" s="58"/>
+      <c r="BG3" s="58"/>
+      <c r="BH3" s="58"/>
+      <c r="BI3" s="58"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58"/>
+      <c r="AE4" s="58"/>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="58"/>
+      <c r="AH4" s="58"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="58"/>
+      <c r="AR4" s="58"/>
+      <c r="AS4" s="58"/>
+      <c r="AT4" s="58"/>
+      <c r="AU4" s="58"/>
+      <c r="AV4" s="58"/>
+      <c r="AW4" s="58"/>
+      <c r="AX4" s="58"/>
+      <c r="AY4" s="58"/>
+      <c r="AZ4" s="58"/>
+      <c r="BA4" s="58"/>
+      <c r="BB4" s="58"/>
+      <c r="BC4" s="58"/>
+      <c r="BD4" s="58"/>
+      <c r="BE4" s="58"/>
+      <c r="BF4" s="58"/>
+      <c r="BG4" s="58"/>
+      <c r="BH4" s="58"/>
+      <c r="BI4" s="58"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="T5" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF5" s="26"/>
+      <c r="AG5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH5" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT5" s="26"/>
+      <c r="AU5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV5" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ5" s="17"/>
+      <c r="BA5" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="BE5" s="24"/>
+      <c r="BF5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH5" s="26"/>
+      <c r="BI5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="BJ5" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" s="37" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="R6" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" s="19"/>
+      <c r="T6" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="V6" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="W6" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="X6" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z6" s="45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA6" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB6" s="46" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC6" s="46" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD6" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE6" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF6" s="50" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="40" t="n">
+        <v>37</v>
+      </c>
+      <c r="AH6" s="42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI6" s="42" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ6" s="42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK6" s="40" t="n">
+        <v>41</v>
+      </c>
+      <c r="AL6" s="40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN6" s="45" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO6" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP6" s="46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ6" s="46" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR6" s="40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS6" s="49" t="n">
+        <v>51</v>
+      </c>
+      <c r="AT6" s="50" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU6" s="40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AV6" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="AW6" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX6" s="42" t="n">
+        <v>56</v>
+      </c>
+      <c r="AY6" s="40" t="n">
+        <v>57</v>
+      </c>
+      <c r="AZ6" s="40" t="n">
+        <v>58</v>
+      </c>
+      <c r="BA6" s="45" t="n">
+        <v>59</v>
+      </c>
+      <c r="BB6" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC6" s="45" t="n">
+        <v>61</v>
+      </c>
+      <c r="BD6" s="46" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE6" s="46" t="n">
+        <v>63</v>
+      </c>
+      <c r="BF6" s="40" t="n">
+        <v>64</v>
+      </c>
+      <c r="BG6" s="49" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH6" s="50" t="n">
+        <v>66</v>
+      </c>
+      <c r="BI6" s="40" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="55"/>
+      <c r="O7" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" s="57"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="V7" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="W7" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y7" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA7" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB7" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC7" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF7" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI7" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ7" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK7" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL7" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM7" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN7" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO7" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP7" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ7" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR7" s="17"/>
+      <c r="AS7" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="AT7" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU7" s="17"/>
+      <c r="AV7" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AW7" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AX7" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY7" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ7" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="BA7" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="BB7" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC7" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="BD7" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="BE7" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF7" s="17"/>
+      <c r="BG7" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="BH7" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="BI7" s="17"/>
+      <c r="BJ7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="O8" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="P8" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="R8" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="S8" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="T8" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="U8" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="V8" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="W8" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="X8" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y8" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z8" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA8" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB8" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC8" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD8" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF8" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG8" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH8" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI8" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ8" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM8" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN8" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO8" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP8" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="AQ8" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV8" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW8" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX8" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA8" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="BB8" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="BC8" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD8" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="BE8" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="BJ8" s="67" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="T3:AG4"/>
+    <mergeCell ref="AH3:AU4"/>
+    <mergeCell ref="AV3:BI4"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5:AA5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="AK5:AL5"/>
+    <mergeCell ref="AM5:AO5"/>
+    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="AS5:AT5"/>
+    <mergeCell ref="AV5:AX5"/>
+    <mergeCell ref="AY5:AZ5"/>
+    <mergeCell ref="BA5:BC5"/>
+    <mergeCell ref="BD5:BE5"/>
+    <mergeCell ref="BG5:BH5"/>
+    <mergeCell ref="BJ5:BJ7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:R7"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/excel_templates/templates.xlsx
+++ b/excel_templates/templates.xlsx
@@ -567,7 +567,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="246">
   <si>
     <t xml:space="preserve">FHB STAT</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t xml:space="preserve">ФУТБОЛ 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФУТБОЛ ИСХОД</t>
   </si>
   <si>
     <t xml:space="preserve">ИСХОД МАТЧА</t>
@@ -1659,7 +1662,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1745,6 +1748,13 @@
       <bottom style="medium"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1774,7 +1784,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="112">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2209,6 +2219,18 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7316,7 +7338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BJ9"/>
+  <dimension ref="A1:BJ21"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="6.71"/>
@@ -7471,7 +7493,7 @@
       <c r="AT3" s="58"/>
       <c r="AU3" s="58"/>
       <c r="AV3" s="58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AW3" s="58"/>
       <c r="AX3" s="58"/>
@@ -7486,6 +7508,7 @@
       <c r="BG3" s="58"/>
       <c r="BH3" s="58"/>
       <c r="BI3" s="58"/>
+      <c r="BJ3" s="109"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
@@ -7551,6 +7574,7 @@
       <c r="BG4" s="58"/>
       <c r="BH4" s="58"/>
       <c r="BI4" s="58"/>
+      <c r="BJ4" s="110"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
@@ -7593,7 +7617,7 @@
         <v>14</v>
       </c>
       <c r="T5" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="U5" s="20"/>
       <c r="V5" s="20"/>
@@ -7621,7 +7645,7 @@
         <v>25</v>
       </c>
       <c r="AH5" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AI5" s="20"/>
       <c r="AJ5" s="20"/>
@@ -7649,7 +7673,7 @@
         <v>25</v>
       </c>
       <c r="AV5" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AW5" s="20"/>
       <c r="AX5" s="20"/>
@@ -8200,6 +8224,9 @@
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="BJ21" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="29">
